--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06304999999999999</v>
+        <v>0.0963</v>
       </c>
       <c r="E2">
-        <v>0.0376</v>
+        <v>0.0902</v>
       </c>
       <c r="F2">
-        <v>0.145</v>
+        <v>0.215</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>4.224992967921499e-05</v>
+        <v>3.014802229223782e-05</v>
       </c>
       <c r="J2">
-        <v>3.682411653646132e-05</v>
+        <v>2.679367103081744e-05</v>
       </c>
       <c r="K2">
-        <v>12073</v>
+        <v>15524.6</v>
       </c>
       <c r="L2">
-        <v>0.5211246935322352</v>
+        <v>0.552762101440245</v>
       </c>
       <c r="M2">
-        <v>6160.999999999999</v>
+        <v>5736.900000000001</v>
       </c>
       <c r="N2">
-        <v>0.0232840617743808</v>
+        <v>0.02294207554820799</v>
       </c>
       <c r="O2">
-        <v>0.5103122670421602</v>
+        <v>0.3695360911070173</v>
       </c>
       <c r="P2">
-        <v>5410.5</v>
+        <v>5554.8</v>
       </c>
       <c r="Q2">
-        <v>0.02044772216041022</v>
+        <v>0.02221385090470215</v>
       </c>
       <c r="R2">
-        <v>0.4481487616996604</v>
+        <v>0.3578063202916661</v>
       </c>
       <c r="S2">
-        <v>750.4999999999998</v>
+        <v>182.1000000000001</v>
       </c>
       <c r="T2">
-        <v>0.1218146404804415</v>
+        <v>0.03174188150394813</v>
       </c>
       <c r="U2">
-        <v>31525.6</v>
+        <v>33965.8</v>
       </c>
       <c r="V2">
-        <v>0.1191436484133127</v>
+        <v>0.1358304920175221</v>
       </c>
       <c r="W2">
-        <v>0.08953347668000719</v>
+        <v>0.09908389010908036</v>
       </c>
       <c r="X2">
-        <v>0.04613684430364658</v>
+        <v>0.07491531691886319</v>
       </c>
       <c r="Y2">
-        <v>0.04339663237636061</v>
+        <v>0.02416857319021717</v>
       </c>
       <c r="Z2">
-        <v>0.2396199395482924</v>
+        <v>0.2080718491951668</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04364440668301919</v>
+        <v>0.07080719358877985</v>
       </c>
       <c r="AC2">
-        <v>-0.04364440668301919</v>
+        <v>-0.07080719358877985</v>
       </c>
       <c r="AD2">
-        <v>52677.3</v>
+        <v>72153.89999999999</v>
       </c>
       <c r="AE2">
-        <v>1.305937145678451</v>
+        <v>1.516388599556773</v>
       </c>
       <c r="AF2">
-        <v>52678.60593714568</v>
+        <v>72155.41638859955</v>
       </c>
       <c r="AG2">
-        <v>21153.00593714568</v>
+        <v>38189.61638859956</v>
       </c>
       <c r="AH2">
-        <v>0.1660318070632541</v>
+        <v>0.2239351934500233</v>
       </c>
       <c r="AI2">
-        <v>0.2981150804909014</v>
+        <v>0.3531984733580131</v>
       </c>
       <c r="AJ2">
-        <v>0.07402507430378386</v>
+        <v>0.1324879122806268</v>
       </c>
       <c r="AK2">
-        <v>0.1457019222488782</v>
+        <v>0.2242153423444514</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>42481.6935483871</v>
+        <v>62742.52173913043</v>
       </c>
       <c r="AP2">
-        <v>17058.87575576264</v>
+        <v>33208.36207704309</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al Rajhi Banking and Investment Corporation (SASE:1120)</t>
+          <t>Bank AlJazira (SASE:1020)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.117</v>
+        <v>0.0721</v>
       </c>
       <c r="E3">
-        <v>0.115</v>
-      </c>
-      <c r="F3">
-        <v>0.209</v>
+        <v>0.0604</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,34 +731,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.001000972077182463</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.0008680653947104836</v>
       </c>
       <c r="K3">
-        <v>3693.9</v>
+        <v>291.2</v>
       </c>
       <c r="L3">
-        <v>0.6199170960108749</v>
+        <v>0.3442487291642038</v>
       </c>
       <c r="M3">
-        <v>1599.6</v>
+        <v>157.5</v>
       </c>
       <c r="N3">
-        <v>0.01694087743916969</v>
+        <v>0.03782874984988591</v>
       </c>
       <c r="O3">
-        <v>0.4330382522537156</v>
+        <v>0.5408653846153846</v>
       </c>
       <c r="P3">
-        <v>1599.6</v>
+        <v>157.5</v>
       </c>
       <c r="Q3">
-        <v>0.01694087743916969</v>
+        <v>0.03782874984988591</v>
       </c>
       <c r="R3">
-        <v>0.4330382522537156</v>
+        <v>0.5408653846153846</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,61 +767,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3877.2</v>
+        <v>460.2</v>
       </c>
       <c r="V3">
-        <v>0.04106224681617199</v>
+        <v>0.1105320043232857</v>
       </c>
       <c r="W3">
-        <v>0.2522880013113321</v>
+        <v>0.07990341345626166</v>
       </c>
       <c r="X3">
-        <v>0.04285199133200564</v>
+        <v>0.09058641637332329</v>
       </c>
       <c r="Y3">
-        <v>0.2094360099793265</v>
+        <v>-0.01068300291706163</v>
       </c>
       <c r="Z3">
-        <v>0.6583253234342028</v>
+        <v>0.1597871854987443</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.0001387057262496447</v>
       </c>
       <c r="AB3">
-        <v>0.04285199133200564</v>
+        <v>0.07024406530080773</v>
       </c>
       <c r="AC3">
-        <v>-0.04285199133200564</v>
+        <v>-0.07010535957455809</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3319.7</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.516388599556773</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>3321.216388599556</v>
       </c>
       <c r="AG3">
-        <v>-3877.2</v>
+        <v>2861.016388599557</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.443733097710731</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.4771165880371862</v>
       </c>
       <c r="AJ3">
-        <v>-0.04282055501500354</v>
+        <v>0.4072901578310565</v>
       </c>
       <c r="AK3">
-        <v>-0.2962295144592581</v>
+        <v>0.4401010915516556</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>2886.695652173913</v>
+      </c>
+      <c r="AP3">
+        <v>2487.840337912658</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bank Albilad (SASE:1140)</t>
+          <t>The Saudi British Bank (SASE:1060)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,13 +847,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.116</v>
+        <v>0.0766</v>
       </c>
       <c r="E4">
-        <v>0.157</v>
-      </c>
-      <c r="F4">
-        <v>0.121</v>
+        <v>0.00278</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,82 +865,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>436.3</v>
+        <v>1040.5</v>
       </c>
       <c r="L4">
-        <v>0.4144580602260853</v>
+        <v>0.4590171166401976</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>555.9</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02610079725047187</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.5342623738587218</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>555.9</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02610079725047187</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.5342623738587218</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>1214.1</v>
+        <v>558.2</v>
       </c>
       <c r="V4">
-        <v>0.131125055350952</v>
+        <v>0.02620878759707393</v>
       </c>
       <c r="W4">
-        <v>0.1587180326676125</v>
+        <v>0.07434054471149724</v>
       </c>
       <c r="X4">
-        <v>0.04477983321995867</v>
+        <v>0.07986806215709041</v>
       </c>
       <c r="Y4">
-        <v>0.1139381994476538</v>
+        <v>-0.005527517445593169</v>
       </c>
       <c r="Z4">
-        <v>0.4138947865062515</v>
+        <v>0.1401924646859461</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04307701007984467</v>
+        <v>0.07030923195042939</v>
       </c>
       <c r="AC4">
-        <v>-0.04307701007984467</v>
+        <v>-0.07030923195042939</v>
       </c>
       <c r="AD4">
-        <v>804</v>
+        <v>7963</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>804</v>
+        <v>7963</v>
       </c>
       <c r="AG4">
-        <v>-410.0999999999999</v>
+        <v>7404.8</v>
       </c>
       <c r="AH4">
-        <v>0.07989585714143753</v>
+        <v>0.2721351140759777</v>
       </c>
       <c r="AI4">
-        <v>0.2026260742458227</v>
+        <v>0.3589151863988137</v>
       </c>
       <c r="AJ4">
-        <v>-0.0463442196858402</v>
+        <v>0.2579800020903739</v>
       </c>
       <c r="AK4">
-        <v>-0.1489214903043067</v>
+        <v>0.3423694175632626</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -966,13 +969,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.114</v>
+        <v>0.129</v>
       </c>
       <c r="E5">
-        <v>0.106</v>
+        <v>0.128</v>
       </c>
       <c r="F5">
-        <v>0.205</v>
+        <v>0.25</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -987,28 +990,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>662.3</v>
+        <v>893.8</v>
       </c>
       <c r="L5">
-        <v>0.4936274875158381</v>
+        <v>0.5202561117578579</v>
       </c>
       <c r="M5">
-        <v>344.4</v>
+        <v>463.5</v>
       </c>
       <c r="N5">
-        <v>0.02698277145341868</v>
+        <v>0.02675479104132995</v>
       </c>
       <c r="O5">
-        <v>0.5200060395591122</v>
+        <v>0.518572387558738</v>
       </c>
       <c r="P5">
-        <v>344.4</v>
+        <v>463.5</v>
       </c>
       <c r="Q5">
-        <v>0.02698277145341868</v>
+        <v>0.02675479104132995</v>
       </c>
       <c r="R5">
-        <v>0.5200060395591122</v>
+        <v>0.518572387558738</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1017,55 +1020,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>943.7</v>
+        <v>844.6</v>
       </c>
       <c r="V5">
-        <v>0.0739362410586272</v>
+        <v>0.04875317478642346</v>
       </c>
       <c r="W5">
-        <v>0.1033422793658719</v>
+        <v>0.1111428891182432</v>
       </c>
       <c r="X5">
-        <v>0.04607515953170988</v>
+        <v>0.07554110126137241</v>
       </c>
       <c r="Y5">
-        <v>0.05726711983416203</v>
+        <v>0.03560178785687079</v>
       </c>
       <c r="Z5">
-        <v>0.1967561701690839</v>
+        <v>0.191929573688444</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04320903433718635</v>
+        <v>0.07034855144595863</v>
       </c>
       <c r="AC5">
-        <v>-0.04320903433718635</v>
+        <v>-0.07034855144595863</v>
       </c>
       <c r="AD5">
-        <v>1853</v>
+        <v>3513.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1853</v>
+        <v>3513.1</v>
       </c>
       <c r="AG5">
-        <v>909.3</v>
+        <v>2668.5</v>
       </c>
       <c r="AH5">
-        <v>0.1267728009742281</v>
+        <v>0.1685983174242097</v>
       </c>
       <c r="AI5">
-        <v>0.1872681886628465</v>
+        <v>0.2965817666078528</v>
       </c>
       <c r="AJ5">
-        <v>0.06650332772617568</v>
+        <v>0.1334750531449294</v>
       </c>
       <c r="AK5">
-        <v>0.1015841451425507</v>
+        <v>0.2425754724699337</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1082,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banque Saudi Fransi (SASE:1050)</t>
+          <t>Bank Albilad (SASE:1140)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,13 +1094,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0239</v>
+        <v>0.116</v>
       </c>
       <c r="E6">
-        <v>-0.09</v>
+        <v>0.16</v>
       </c>
       <c r="F6">
-        <v>0.182</v>
+        <v>0.2</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,85 +1115,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>680</v>
+        <v>524.4</v>
       </c>
       <c r="L6">
-        <v>0.4628999319264806</v>
+        <v>0.4420839656044512</v>
       </c>
       <c r="M6">
-        <v>335.9</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.02224915878441035</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.4939705882352941</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>335.9</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.02224915878441035</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.4939705882352941</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>1723.5</v>
+        <v>1866.9</v>
       </c>
       <c r="V6">
-        <v>0.1141602416342103</v>
+        <v>0.1578279946232468</v>
       </c>
       <c r="W6">
-        <v>0.07572467399414248</v>
+        <v>0.16574480862227</v>
       </c>
       <c r="X6">
-        <v>0.04434889152419218</v>
+        <v>0.07213689655990643</v>
       </c>
       <c r="Y6">
-        <v>0.0313757824699503</v>
+        <v>0.09360791206236355</v>
       </c>
       <c r="Z6">
-        <v>0.1618964700177436</v>
+        <v>0.4307502360374755</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04332063997707847</v>
+        <v>0.07038833877286754</v>
       </c>
       <c r="AC6">
-        <v>-0.04332063997707847</v>
+        <v>-0.07038833877286754</v>
       </c>
       <c r="AD6">
-        <v>1017.9</v>
+        <v>806.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1017.9</v>
+        <v>806.5</v>
       </c>
       <c r="AG6">
-        <v>-705.6</v>
+        <v>-1060.4</v>
       </c>
       <c r="AH6">
-        <v>0.06316436137535603</v>
+        <v>0.06382961884259845</v>
       </c>
       <c r="AI6">
-        <v>0.08866801975626966</v>
+        <v>0.1886064404480718</v>
       </c>
       <c r="AJ6">
-        <v>-0.04902860001667639</v>
+        <v>-0.0984742252723271</v>
       </c>
       <c r="AK6">
-        <v>-0.07232175802550121</v>
+        <v>-0.4401461065913997</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Saudi British Bank (SASE:1060)</t>
+          <t>Al Rajhi Banking and Investment Corporation (SASE:1120)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,13 +1216,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.051</v>
+        <v>0.134</v>
       </c>
       <c r="E7">
-        <v>-0.038</v>
-      </c>
-      <c r="F7">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1237,85 +1234,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>928.5</v>
+        <v>4460.9</v>
       </c>
       <c r="L7">
-        <v>0.4350780188369805</v>
+        <v>0.6463854636083056</v>
       </c>
       <c r="M7">
-        <v>303</v>
+        <v>30.8</v>
       </c>
       <c r="N7">
-        <v>0.01677647970765738</v>
+        <v>0.0003847749066795924</v>
       </c>
       <c r="O7">
-        <v>0.3263327948303716</v>
+        <v>0.006904436324508508</v>
       </c>
       <c r="P7">
-        <v>272.3</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.01507668456896074</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.2932687129779214</v>
+        <v>-0</v>
       </c>
       <c r="S7">
-        <v>30.69999999999999</v>
+        <v>30.8</v>
       </c>
       <c r="T7">
-        <v>0.1013201320132013</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>2142.8</v>
+        <v>5666.7</v>
       </c>
       <c r="V7">
-        <v>0.1186423786058358</v>
+        <v>0.07079233648315734</v>
       </c>
       <c r="W7">
-        <v>0.0700411119073662</v>
+        <v>0.2629363951973688</v>
       </c>
       <c r="X7">
-        <v>0.05103822182978501</v>
+        <v>0.07041257893186294</v>
       </c>
       <c r="Y7">
-        <v>0.01900289007758119</v>
+        <v>0.1925238162655059</v>
       </c>
       <c r="Z7">
-        <v>0.2054963360969081</v>
+        <v>0.5272796729953776</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04361070658654662</v>
+        <v>0.07041257893186294</v>
       </c>
       <c r="AC7">
-        <v>-0.04361070658654662</v>
+        <v>-0.07041257893186294</v>
       </c>
       <c r="AD7">
-        <v>6659.5</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>6659.5</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>4516.7</v>
+        <v>-5666.7</v>
       </c>
       <c r="AH7">
-        <v>0.2693918003276633</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.3219778466477463</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0.2000513781297475</v>
+        <v>-0.07618570020744796</v>
       </c>
       <c r="AK7">
-        <v>0.2436152597315038</v>
+        <v>-0.328464360860417</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1341,13 +1338,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.07820000000000001</v>
+        <v>0.132</v>
       </c>
       <c r="E8">
-        <v>0.06280000000000001</v>
-      </c>
-      <c r="F8">
-        <v>0.133</v>
+        <v>0.151</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1362,28 +1356,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>1409.7</v>
+        <v>1759.2</v>
       </c>
       <c r="L8">
-        <v>0.5265575974899149</v>
+        <v>0.5669900409320915</v>
       </c>
       <c r="M8">
-        <v>799.4</v>
+        <v>827.4</v>
       </c>
       <c r="N8">
-        <v>0.03691594395648038</v>
+        <v>0.03259122707506144</v>
       </c>
       <c r="O8">
-        <v>0.5670710080158898</v>
+        <v>0.4703274215552524</v>
       </c>
       <c r="P8">
-        <v>799.4</v>
+        <v>827.4</v>
       </c>
       <c r="Q8">
-        <v>0.03691594395648038</v>
+        <v>0.03259122707506144</v>
       </c>
       <c r="R8">
-        <v>0.5670710080158898</v>
+        <v>0.4703274215552524</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1392,55 +1386,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>8840.6</v>
+        <v>8314.299999999999</v>
       </c>
       <c r="V8">
-        <v>0.408255058971304</v>
+        <v>0.3274996848805697</v>
       </c>
       <c r="W8">
-        <v>0.1239645438716826</v>
+        <v>0.1432923352610573</v>
       </c>
       <c r="X8">
-        <v>0.04563372649707902</v>
+        <v>0.07347810452419362</v>
       </c>
       <c r="Y8">
-        <v>0.07833081737460357</v>
+        <v>0.06981423073686363</v>
       </c>
       <c r="Z8">
-        <v>1.898050336760014</v>
+        <v>0.5045368804475088</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04367810677949176</v>
+        <v>0.07120180824569677</v>
       </c>
       <c r="AC8">
-        <v>-0.04367810677949176</v>
+        <v>-0.07120180824569677</v>
       </c>
       <c r="AD8">
-        <v>2713.2</v>
+        <v>3077.3</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2713.2</v>
+        <v>3077.3</v>
       </c>
       <c r="AG8">
-        <v>-6127.400000000001</v>
+        <v>-5236.999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.1113436584344914</v>
+        <v>0.1081101020569481</v>
       </c>
       <c r="AI8">
-        <v>0.1809982521914317</v>
+        <v>0.1890384367302057</v>
       </c>
       <c r="AJ8">
-        <v>-0.3946236282137154</v>
+        <v>-0.2598981647824835</v>
       </c>
       <c r="AK8">
-        <v>-0.9963900091062835</v>
+        <v>-0.6575511024057052</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1457,7 +1451,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bank AlJazira (SASE:1020)</t>
+          <t>Arab National Bank (SASE:1080)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1466,13 +1460,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0349</v>
+        <v>0.0135</v>
       </c>
       <c r="E9">
-        <v>-0.203</v>
+        <v>-0.0155</v>
       </c>
       <c r="F9">
-        <v>0.138</v>
+        <v>0.21</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1481,34 +1475,34 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.001800943092666623</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0.001711237456950991</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>75.2</v>
+        <v>728.2</v>
       </c>
       <c r="L9">
-        <v>0.13836246550138</v>
+        <v>0.4972006008466476</v>
       </c>
       <c r="M9">
-        <v>77.2</v>
+        <v>363.6</v>
       </c>
       <c r="N9">
-        <v>0.01831423623466895</v>
+        <v>0.02842090452889771</v>
       </c>
       <c r="O9">
-        <v>1.026595744680851</v>
+        <v>0.4993133754463059</v>
       </c>
       <c r="P9">
-        <v>77.2</v>
+        <v>363.6</v>
       </c>
       <c r="Q9">
-        <v>0.01831423623466895</v>
+        <v>0.02842090452889771</v>
       </c>
       <c r="R9">
-        <v>1.026595744680851</v>
+        <v>0.4993133754463059</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1517,67 +1511,61 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>643.4</v>
+        <v>866.1</v>
       </c>
       <c r="V9">
-        <v>0.1526344506915285</v>
+        <v>0.06769896978129349</v>
       </c>
       <c r="W9">
-        <v>0.02390033053648614</v>
+        <v>0.08884171485737989</v>
       </c>
       <c r="X9">
-        <v>0.05492746027504736</v>
+        <v>0.0734971861928118</v>
       </c>
       <c r="Y9">
-        <v>-0.03102712973856121</v>
+        <v>0.01534452866456809</v>
       </c>
       <c r="Z9">
-        <v>0.08002879049039395</v>
+        <v>0.1649937476765014</v>
       </c>
       <c r="AA9">
-        <v>0.0001369482639216454</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04384418136142212</v>
+        <v>0.07120618682983026</v>
       </c>
       <c r="AC9">
-        <v>-0.04370723309750048</v>
+        <v>-0.07120618682983026</v>
       </c>
       <c r="AD9">
-        <v>2291.4</v>
+        <v>1560.4</v>
       </c>
       <c r="AE9">
-        <v>1.305937145678451</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>2292.705937145678</v>
+        <v>1560.4</v>
       </c>
       <c r="AG9">
-        <v>1649.305937145678</v>
+        <v>694.3000000000001</v>
       </c>
       <c r="AH9">
-        <v>0.3522900807541715</v>
+        <v>0.108709888670596</v>
       </c>
       <c r="AI9">
-        <v>0.3861655765313696</v>
+        <v>0.1557689620061094</v>
       </c>
       <c r="AJ9">
-        <v>0.2812304790504647</v>
+        <v>0.05147653046850094</v>
       </c>
       <c r="AK9">
-        <v>0.3115597951092407</v>
+        <v>0.07586900221826409</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>1847.903225806452</v>
-      </c>
-      <c r="AP9">
-        <v>1330.085433181999</v>
       </c>
     </row>
     <row r="10">
@@ -1588,7 +1576,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arab National Bank (SASE:1080)</t>
+          <t>Banque Saudi Fransi (SASE:1050)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1597,13 +1585,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0257</v>
+        <v>0.0278</v>
       </c>
       <c r="E10">
-        <v>-0.0711</v>
-      </c>
-      <c r="F10">
-        <v>0.122</v>
+        <v>0.0103</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1618,85 +1603,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>531.6</v>
+        <v>975.8</v>
       </c>
       <c r="L10">
-        <v>0.4458983392048314</v>
+        <v>0.5579826166514181</v>
       </c>
       <c r="M10">
-        <v>178.6</v>
+        <v>525.7</v>
       </c>
       <c r="N10">
-        <v>0.01955481589348866</v>
+        <v>0.0405645235964073</v>
       </c>
       <c r="O10">
-        <v>0.335966892400301</v>
+        <v>0.5387374461979915</v>
       </c>
       <c r="P10">
-        <v>178.6</v>
+        <v>511.5</v>
       </c>
       <c r="Q10">
-        <v>0.01955481589348866</v>
+        <v>0.03946881076576438</v>
       </c>
       <c r="R10">
-        <v>0.335966892400301</v>
+        <v>0.5241852838696455</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>14.20000000000005</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>0.02701160357618422</v>
       </c>
       <c r="U10">
-        <v>696.6</v>
+        <v>1946.5</v>
       </c>
       <c r="V10">
-        <v>0.07627035135164728</v>
+        <v>0.1501975369610173</v>
       </c>
       <c r="W10">
-        <v>0.06796389577846532</v>
+        <v>0.09327088510800993</v>
       </c>
       <c r="X10">
-        <v>0.04619852907558328</v>
+        <v>0.07428953257635396</v>
       </c>
       <c r="Y10">
-        <v>0.02176536670288204</v>
+        <v>0.01898135253165598</v>
       </c>
       <c r="Z10">
-        <v>0.1423862414905052</v>
+        <v>0.1792464433602558</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04382386955869552</v>
+        <v>0.07138294483304684</v>
       </c>
       <c r="AC10">
-        <v>-0.04382386955869552</v>
+        <v>-0.07138294483304684</v>
       </c>
       <c r="AD10">
-        <v>1376.7</v>
+        <v>1986.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1376.7</v>
+        <v>1986.7</v>
       </c>
       <c r="AG10">
-        <v>680.1</v>
+        <v>40.20000000000005</v>
       </c>
       <c r="AH10">
-        <v>0.1309895337773549</v>
+        <v>0.1329225293216381</v>
       </c>
       <c r="AI10">
-        <v>0.1436981368404572</v>
+        <v>0.1648754740781928</v>
       </c>
       <c r="AJ10">
-        <v>0.0693031976684941</v>
+        <v>0.003092355267004111</v>
       </c>
       <c r="AK10">
-        <v>0.07655421605376019</v>
+        <v>0.003978937366378973</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1722,13 +1707,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0717</v>
+        <v>0.129</v>
       </c>
       <c r="E11">
-        <v>0.06709999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="F11">
-        <v>0.152</v>
+        <v>0.22</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1743,85 +1728,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>3378</v>
+        <v>4466.3</v>
       </c>
       <c r="L11">
-        <v>0.5493933578375565</v>
+        <v>0.5564442783280384</v>
       </c>
       <c r="M11">
-        <v>2450.9</v>
+        <v>2383.9</v>
       </c>
       <c r="N11">
-        <v>0.03221159848858222</v>
+        <v>0.03996854692142095</v>
       </c>
       <c r="O11">
-        <v>0.7255476613380698</v>
+        <v>0.5337527707498376</v>
       </c>
       <c r="P11">
-        <v>1731.1</v>
+        <v>2383.9</v>
       </c>
       <c r="Q11">
-        <v>0.02275143748973222</v>
+        <v>0.03996854692142095</v>
       </c>
       <c r="R11">
-        <v>0.5124629958555358</v>
+        <v>0.5337527707498376</v>
       </c>
       <c r="S11">
-        <v>719.7999999999997</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>0.2936880329674812</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>10900.5</v>
+        <v>12440.3</v>
       </c>
       <c r="V11">
-        <v>0.1432626909807787</v>
+        <v>0.2085744847797949</v>
       </c>
       <c r="W11">
-        <v>0.1669203249461388</v>
+        <v>0.1048968951101508</v>
       </c>
       <c r="X11">
-        <v>0.05232146134689722</v>
+        <v>0.09009425074104868</v>
       </c>
       <c r="Y11">
-        <v>0.1145988635992416</v>
+        <v>0.0148026443691021</v>
       </c>
       <c r="Z11">
-        <v>0.1856069067527998</v>
+        <v>0.1419966033329795</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.04479864186856101</v>
+        <v>0.0729422727057177</v>
       </c>
       <c r="AC11">
-        <v>-0.04479864186856101</v>
+        <v>-0.0729422727057177</v>
       </c>
       <c r="AD11">
-        <v>32453</v>
+        <v>46417.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>32453</v>
+        <v>46417.5</v>
       </c>
       <c r="AG11">
-        <v>21552.5</v>
+        <v>33977.2</v>
       </c>
       <c r="AH11">
-        <v>0.298994384584556</v>
+        <v>0.4376453750121392</v>
       </c>
       <c r="AI11">
-        <v>0.4312771267505309</v>
+        <v>0.5165868707305835</v>
       </c>
       <c r="AJ11">
-        <v>0.220734330192544</v>
+        <v>0.3629205226144394</v>
       </c>
       <c r="AK11">
-        <v>0.3349360742586028</v>
+        <v>0.4389030910469567</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1847,13 +1832,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0544</v>
+        <v>0.0645</v>
       </c>
       <c r="E12">
-        <v>0.0124</v>
-      </c>
-      <c r="F12">
-        <v>0.0867</v>
+        <v>0.0119</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1868,85 +1850,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>277.5</v>
+        <v>384.3</v>
       </c>
       <c r="L12">
-        <v>0.4272517321016167</v>
+        <v>0.4659876318661331</v>
       </c>
       <c r="M12">
-        <v>72</v>
+        <v>428.6</v>
       </c>
       <c r="N12">
-        <v>0.01842657521625633</v>
+        <v>0.09288314840499308</v>
       </c>
       <c r="O12">
-        <v>0.2594594594594595</v>
+        <v>1.115274525110591</v>
       </c>
       <c r="P12">
-        <v>72</v>
+        <v>291.5</v>
       </c>
       <c r="Q12">
-        <v>0.01842657521625633</v>
+        <v>0.06317180998613038</v>
       </c>
       <c r="R12">
-        <v>0.2594594594594595</v>
+        <v>0.7585219880301848</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>137.1</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>0.3198786747550164</v>
       </c>
       <c r="U12">
-        <v>543.2</v>
+        <v>1002</v>
       </c>
       <c r="V12">
-        <v>0.1390182730204228</v>
+        <v>0.2171463245492372</v>
       </c>
       <c r="W12">
-        <v>0.07029765674477517</v>
+        <v>0.08637702007147513</v>
       </c>
       <c r="X12">
-        <v>0.062787628694441</v>
+        <v>0.08964813168449112</v>
       </c>
       <c r="Y12">
-        <v>0.007510028050334169</v>
+        <v>-0.003271111613015992</v>
       </c>
       <c r="Z12">
-        <v>0.07130545522412637</v>
+        <v>0.1112279991907748</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.04708541670061003</v>
+        <v>0.07422301751205507</v>
       </c>
       <c r="AC12">
-        <v>-0.04708541670061003</v>
+        <v>-0.07422301751205507</v>
       </c>
       <c r="AD12">
-        <v>3508.6</v>
+        <v>3509.7</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>3508.6</v>
+        <v>3509.7</v>
       </c>
       <c r="AG12">
-        <v>2965.4</v>
+        <v>2507.7</v>
       </c>
       <c r="AH12">
-        <v>0.4731121898597627</v>
+        <v>0.4320109304415258</v>
       </c>
       <c r="AI12">
-        <v>0.4409062920190507</v>
+        <v>0.4440466099014411</v>
       </c>
       <c r="AJ12">
-        <v>0.4314689791642417</v>
+        <v>0.3521012061049409</v>
       </c>
       <c r="AK12">
-        <v>0.3999460516555398</v>
+        <v>0.3633347339138498</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_bank_money_center.xlsx
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0963</v>
+        <v>0.115</v>
       </c>
       <c r="E2">
-        <v>0.0902</v>
+        <v>0.12</v>
       </c>
       <c r="F2">
-        <v>0.215</v>
+        <v>0.09744999999999998</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,103 +603,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>3.014802229223782e-05</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>2.679367103081744e-05</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>15524.6</v>
+        <v>18334.1</v>
       </c>
       <c r="L2">
-        <v>0.552762101440245</v>
+        <v>0.5761725931396426</v>
       </c>
       <c r="M2">
-        <v>5736.900000000001</v>
+        <v>9386.207</v>
       </c>
       <c r="N2">
-        <v>0.02294207554820799</v>
+        <v>0.0357187293911168</v>
       </c>
       <c r="O2">
-        <v>0.3695360911070173</v>
+        <v>0.5119535183074163</v>
       </c>
       <c r="P2">
-        <v>5554.8</v>
+        <v>8562.227000000001</v>
       </c>
       <c r="Q2">
-        <v>0.02221385090470215</v>
+        <v>0.03258311575680291</v>
       </c>
       <c r="R2">
-        <v>0.3578063202916661</v>
+        <v>0.4670110340840293</v>
       </c>
       <c r="S2">
-        <v>182.1000000000001</v>
+        <v>823.9800000000002</v>
       </c>
       <c r="T2">
-        <v>0.03174188150394813</v>
+        <v>0.08778625913534617</v>
       </c>
       <c r="U2">
-        <v>33965.8</v>
+        <v>28854</v>
       </c>
       <c r="V2">
-        <v>0.1358304920175221</v>
+        <v>0.1098024172971344</v>
       </c>
       <c r="W2">
-        <v>0.09908389010908036</v>
+        <v>0.1229374576615149</v>
       </c>
       <c r="X2">
-        <v>0.07491531691886319</v>
+        <v>0.06712200636388879</v>
       </c>
       <c r="Y2">
-        <v>0.02416857319021717</v>
+        <v>0.05581545129762615</v>
       </c>
       <c r="Z2">
-        <v>0.2080718491951668</v>
+        <v>0.2005471409782022</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07080719358877985</v>
+        <v>0.06139199548169854</v>
       </c>
       <c r="AC2">
-        <v>-0.07080719358877985</v>
+        <v>-0.06139199548169854</v>
       </c>
       <c r="AD2">
-        <v>72153.89999999999</v>
+        <v>92402</v>
       </c>
       <c r="AE2">
-        <v>1.516388599556773</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>72155.41638859955</v>
+        <v>92402</v>
       </c>
       <c r="AG2">
-        <v>38189.61638859956</v>
+        <v>63548</v>
       </c>
       <c r="AH2">
-        <v>0.2239351934500233</v>
+        <v>0.2601531435476519</v>
       </c>
       <c r="AI2">
-        <v>0.3531984733580131</v>
+        <v>0.3916804465399554</v>
       </c>
       <c r="AJ2">
-        <v>0.1324879122806268</v>
+        <v>0.194735927626436</v>
       </c>
       <c r="AK2">
-        <v>0.2242153423444514</v>
+        <v>0.3069096198789034</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>62742.52173913043</v>
-      </c>
-      <c r="AP2">
-        <v>33208.36207704309</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0721</v>
+        <v>0.0425</v>
       </c>
       <c r="E3">
-        <v>0.0604</v>
+        <v>0.0132</v>
+      </c>
+      <c r="F3">
+        <v>-0.017</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,103 +728,97 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.001000972077182463</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.0008680653947104836</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>291.2</v>
+        <v>262.5</v>
       </c>
       <c r="L3">
-        <v>0.3442487291642038</v>
+        <v>0.3222836095764273</v>
       </c>
       <c r="M3">
-        <v>157.5</v>
+        <v>13.127</v>
       </c>
       <c r="N3">
-        <v>0.03782874984988591</v>
+        <v>0.00318299750248539</v>
       </c>
       <c r="O3">
-        <v>0.5408653846153846</v>
+        <v>0.05000761904761904</v>
       </c>
       <c r="P3">
-        <v>157.5</v>
+        <v>0.027</v>
       </c>
       <c r="Q3">
-        <v>0.03782874984988591</v>
+        <v>6.546882956281369e-06</v>
       </c>
       <c r="R3">
-        <v>0.5408653846153846</v>
+        <v>0.0001028571428571429</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>13.1</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.9979431705644854</v>
       </c>
       <c r="U3">
-        <v>460.2</v>
+        <v>613.9</v>
       </c>
       <c r="V3">
-        <v>0.1105320043232857</v>
+        <v>0.148856720254116</v>
       </c>
       <c r="W3">
-        <v>0.07990341345626166</v>
+        <v>0.07211934721688004</v>
       </c>
       <c r="X3">
-        <v>0.09058641637332329</v>
+        <v>0.08460486055035688</v>
       </c>
       <c r="Y3">
-        <v>-0.01068300291706163</v>
+        <v>-0.01248551333347683</v>
       </c>
       <c r="Z3">
-        <v>0.1597871854987443</v>
+        <v>0.1253211884356777</v>
       </c>
       <c r="AA3">
-        <v>0.0001387057262496447</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07024406530080773</v>
+        <v>0.06036560673504222</v>
       </c>
       <c r="AC3">
-        <v>-0.07010535957455809</v>
+        <v>-0.06036560673504222</v>
       </c>
       <c r="AD3">
-        <v>3319.7</v>
+        <v>5497.1</v>
       </c>
       <c r="AE3">
-        <v>1.516388599556773</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>3321.216388599556</v>
+        <v>5497.1</v>
       </c>
       <c r="AG3">
-        <v>2861.016388599557</v>
+        <v>4883.200000000001</v>
       </c>
       <c r="AH3">
-        <v>0.443733097710731</v>
+        <v>0.5713528457988608</v>
       </c>
       <c r="AI3">
-        <v>0.4771165880371862</v>
+        <v>0.5579849163088604</v>
       </c>
       <c r="AJ3">
-        <v>0.4072901578310565</v>
+        <v>0.5421380435868685</v>
       </c>
       <c r="AK3">
-        <v>0.4401010915516556</v>
+        <v>0.5286107081772716</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>2886.695652173913</v>
-      </c>
-      <c r="AP3">
-        <v>2487.840337912658</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Saudi British Bank (SASE:1060)</t>
+          <t>Saudi Awwal Bank (SASE:1060)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,10 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0766</v>
+        <v>0.118</v>
       </c>
       <c r="E4">
-        <v>0.00278</v>
+        <v>0.124</v>
+      </c>
+      <c r="F4">
+        <v>0.144</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1040.5</v>
+        <v>1713.3</v>
       </c>
       <c r="L4">
-        <v>0.4590171166401976</v>
+        <v>0.5597373321572087</v>
       </c>
       <c r="M4">
-        <v>555.9</v>
+        <v>932.6800000000001</v>
       </c>
       <c r="N4">
-        <v>0.02610079725047187</v>
+        <v>0.04491142239407525</v>
       </c>
       <c r="O4">
-        <v>0.5342623738587218</v>
+        <v>0.5443763497344307</v>
       </c>
       <c r="P4">
-        <v>555.9</v>
+        <v>922.7</v>
       </c>
       <c r="Q4">
-        <v>0.02610079725047187</v>
+        <v>0.04443085457285804</v>
       </c>
       <c r="R4">
-        <v>0.5342623738587218</v>
+        <v>0.5385513336835347</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>9.980000000000018</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.01070034738602738</v>
       </c>
       <c r="U4">
-        <v>558.2</v>
+        <v>1550.9</v>
       </c>
       <c r="V4">
-        <v>0.02620878759707393</v>
+        <v>0.07468062464186141</v>
       </c>
       <c r="W4">
-        <v>0.07434054471149724</v>
+        <v>0.1206846758003733</v>
       </c>
       <c r="X4">
-        <v>0.07986806215709041</v>
+        <v>0.07026738011906988</v>
       </c>
       <c r="Y4">
-        <v>-0.005527517445593169</v>
+        <v>0.05041729568130345</v>
       </c>
       <c r="Z4">
-        <v>0.1401924646859461</v>
+        <v>0.1591499937606589</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07030923195042939</v>
+        <v>0.0606049642191074</v>
       </c>
       <c r="AC4">
-        <v>-0.07030923195042939</v>
+        <v>-0.0606049642191074</v>
       </c>
       <c r="AD4">
-        <v>7963</v>
+        <v>10891</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>7963</v>
+        <v>10891</v>
       </c>
       <c r="AG4">
-        <v>7404.8</v>
+        <v>9340.1</v>
       </c>
       <c r="AH4">
-        <v>0.2721351140759777</v>
+        <v>0.3440193820854694</v>
       </c>
       <c r="AI4">
-        <v>0.3589151863988137</v>
+        <v>0.4237759679998754</v>
       </c>
       <c r="AJ4">
-        <v>0.2579800020903739</v>
+        <v>0.3102281181909975</v>
       </c>
       <c r="AK4">
-        <v>0.3423694175632626</v>
+        <v>0.3867696384943476</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -969,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="E5">
-        <v>0.128</v>
+        <v>0.131</v>
       </c>
       <c r="F5">
-        <v>0.25</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>893.8</v>
+        <v>1167.6</v>
       </c>
       <c r="L5">
-        <v>0.5202561117578579</v>
+        <v>0.5550484883057615</v>
       </c>
       <c r="M5">
-        <v>463.5</v>
+        <v>601.8</v>
       </c>
       <c r="N5">
-        <v>0.02675479104132995</v>
+        <v>0.02828007518796992</v>
       </c>
       <c r="O5">
-        <v>0.518572387558738</v>
+        <v>0.5154162384378211</v>
       </c>
       <c r="P5">
-        <v>463.5</v>
+        <v>557.4</v>
       </c>
       <c r="Q5">
-        <v>0.02675479104132995</v>
+        <v>0.02619360902255639</v>
       </c>
       <c r="R5">
-        <v>0.518572387558738</v>
+        <v>0.4773895169578623</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>44.39999999999998</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.07377866400797604</v>
       </c>
       <c r="U5">
-        <v>844.6</v>
+        <v>2178.5</v>
       </c>
       <c r="V5">
-        <v>0.04875317478642346</v>
+        <v>0.1023731203007519</v>
       </c>
       <c r="W5">
-        <v>0.1111428891182432</v>
+        <v>0.140131057823864</v>
       </c>
       <c r="X5">
-        <v>0.07554110126137241</v>
+        <v>0.06147669110453449</v>
       </c>
       <c r="Y5">
-        <v>0.03560178785687079</v>
+        <v>0.07865436671932954</v>
       </c>
       <c r="Z5">
-        <v>0.191929573688444</v>
+        <v>0.1912241948239657</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07034855144595863</v>
+        <v>0.06093777334913664</v>
       </c>
       <c r="AC5">
-        <v>-0.07034855144595863</v>
+        <v>-0.06093777334913664</v>
       </c>
       <c r="AD5">
-        <v>3513.1</v>
+        <v>611.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>3513.1</v>
+        <v>611.4</v>
       </c>
       <c r="AG5">
-        <v>2668.5</v>
+        <v>-1567.1</v>
       </c>
       <c r="AH5">
-        <v>0.1685983174242097</v>
+        <v>0.02792877568360178</v>
       </c>
       <c r="AI5">
-        <v>0.2965817666078528</v>
+        <v>0.06413376410858894</v>
       </c>
       <c r="AJ5">
-        <v>0.1334750531449294</v>
+        <v>-0.0794961674842362</v>
       </c>
       <c r="AK5">
-        <v>0.2425754724699337</v>
+        <v>-0.2130746325478945</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1085,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bank Albilad (SASE:1140)</t>
+          <t>Al Rajhi Banking and Investment Corporation (SASE:1120)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1094,13 +1088,13 @@
         </is>
       </c>
       <c r="D6">
+        <v>0.112</v>
+      </c>
+      <c r="E6">
         <v>0.116</v>
       </c>
-      <c r="E6">
-        <v>0.16</v>
-      </c>
       <c r="F6">
-        <v>0.2</v>
+        <v>0.068</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1115,82 +1109,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>524.4</v>
+        <v>4494.2</v>
       </c>
       <c r="L6">
-        <v>0.4420839656044512</v>
+        <v>0.6410303955269652</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>2559.7</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.02764648956438714</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.5695563170308398</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>2559.7</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.02764648956438714</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.5695563170308398</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>1866.9</v>
+        <v>3805.6</v>
       </c>
       <c r="V6">
-        <v>0.1578279946232468</v>
+        <v>0.04110305140689601</v>
       </c>
       <c r="W6">
-        <v>0.16574480862227</v>
+        <v>0.1960922910449064</v>
       </c>
       <c r="X6">
-        <v>0.07213689655990643</v>
+        <v>0.0612259067063206</v>
       </c>
       <c r="Y6">
-        <v>0.09360791206236355</v>
+        <v>0.1348663843385858</v>
       </c>
       <c r="Z6">
-        <v>0.4307502360374755</v>
+        <v>0.4063795132186807</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07038833877286754</v>
+        <v>0.06101889911994734</v>
       </c>
       <c r="AC6">
-        <v>-0.07038833877286754</v>
+        <v>-0.06101889911994734</v>
       </c>
       <c r="AD6">
-        <v>806.5</v>
+        <v>1350.8</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>806.5</v>
+        <v>1350.8</v>
       </c>
       <c r="AG6">
-        <v>-1060.4</v>
+        <v>-2454.8</v>
       </c>
       <c r="AH6">
-        <v>0.06382961884259845</v>
+        <v>0.01437975847796835</v>
       </c>
       <c r="AI6">
-        <v>0.1886064404480718</v>
+        <v>0.04719380624965062</v>
       </c>
       <c r="AJ6">
-        <v>-0.0984742252723271</v>
+        <v>-0.02723560999423068</v>
       </c>
       <c r="AK6">
-        <v>-0.4401461065913997</v>
+        <v>-0.09891686277038136</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1207,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Al Rajhi Banking and Investment Corporation (SASE:1120)</t>
+          <t>Bank Albilad (SASE:1140)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,10 +1213,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.134</v>
+        <v>0.12</v>
       </c>
       <c r="E7">
-        <v>0.14</v>
+        <v>0.187</v>
+      </c>
+      <c r="F7">
+        <v>0.153</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1234,85 +1234,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>4460.9</v>
+        <v>613.7</v>
       </c>
       <c r="L7">
-        <v>0.6463854636083056</v>
+        <v>0.4698361659776451</v>
       </c>
       <c r="M7">
-        <v>30.8</v>
+        <v>146.2</v>
       </c>
       <c r="N7">
-        <v>0.0003847749066795924</v>
+        <v>0.01207595794064444</v>
       </c>
       <c r="O7">
-        <v>0.006904436324508508</v>
+        <v>0.2382271468144044</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>133.3</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.01101043223999934</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.2172071044484276</v>
       </c>
       <c r="S7">
-        <v>30.8</v>
+        <v>12.90000000000001</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>0.08823529411764709</v>
       </c>
       <c r="U7">
-        <v>5666.7</v>
+        <v>1041.1</v>
       </c>
       <c r="V7">
-        <v>0.07079233648315734</v>
+        <v>0.08599370596446594</v>
       </c>
       <c r="W7">
-        <v>0.2629363951973688</v>
+        <v>0.1768791791560987</v>
       </c>
       <c r="X7">
-        <v>0.07041257893186294</v>
+        <v>0.0621579051222878</v>
       </c>
       <c r="Y7">
-        <v>0.1925238162655059</v>
+        <v>0.1147212740338109</v>
       </c>
       <c r="Z7">
-        <v>0.5272796729953776</v>
+        <v>0.5421716752448945</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.07041257893186294</v>
+        <v>0.06119348387358364</v>
       </c>
       <c r="AC7">
-        <v>-0.07041257893186294</v>
+        <v>-0.06119348387358364</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>812.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>812.9</v>
       </c>
       <c r="AG7">
-        <v>-5666.7</v>
+        <v>-228.1999999999999</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.06291990464101055</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.1726195532149834</v>
       </c>
       <c r="AJ7">
-        <v>-0.07618570020744796</v>
+        <v>-0.01921117986277728</v>
       </c>
       <c r="AK7">
-        <v>-0.328464360860417</v>
+        <v>-0.06221204438265039</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1338,10 +1338,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.132</v>
+        <v>0.131</v>
       </c>
       <c r="E8">
-        <v>0.151</v>
+        <v>0.172</v>
+      </c>
+      <c r="F8">
+        <v>0.0706</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1356,85 +1359,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>1759.2</v>
+        <v>2164.9</v>
       </c>
       <c r="L8">
-        <v>0.5669900409320915</v>
+        <v>0.5863441850387303</v>
       </c>
       <c r="M8">
-        <v>827.4</v>
+        <v>1078</v>
       </c>
       <c r="N8">
-        <v>0.03259122707506144</v>
+        <v>0.04694774341621047</v>
       </c>
       <c r="O8">
-        <v>0.4703274215552524</v>
+        <v>0.4979444778049794</v>
       </c>
       <c r="P8">
-        <v>827.4</v>
+        <v>1033.8</v>
       </c>
       <c r="Q8">
-        <v>0.03259122707506144</v>
+        <v>0.04502279883458106</v>
       </c>
       <c r="R8">
-        <v>0.4703274215552524</v>
+        <v>0.4775278303847753</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>44.20000000000005</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.04100185528756962</v>
       </c>
       <c r="U8">
-        <v>8314.299999999999</v>
+        <v>6855.9</v>
       </c>
       <c r="V8">
-        <v>0.3274996848805697</v>
+        <v>0.2985798089862684</v>
       </c>
       <c r="W8">
-        <v>0.1432923352610573</v>
+        <v>0.1639901828593937</v>
       </c>
       <c r="X8">
-        <v>0.07347810452419362</v>
+        <v>0.0646848111822618</v>
       </c>
       <c r="Y8">
-        <v>0.06981423073686363</v>
+        <v>0.09930537167713191</v>
       </c>
       <c r="Z8">
-        <v>0.5045368804475088</v>
+        <v>0.4635879664507055</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.07120180824569677</v>
+        <v>0.06159050708981344</v>
       </c>
       <c r="AC8">
-        <v>-0.07120180824569677</v>
+        <v>-0.06159050708981344</v>
       </c>
       <c r="AD8">
-        <v>3077.3</v>
+        <v>4813.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>3077.3</v>
+        <v>4813.6</v>
       </c>
       <c r="AG8">
-        <v>-5236.999999999999</v>
+        <v>-2042.299999999999</v>
       </c>
       <c r="AH8">
-        <v>0.1081101020569481</v>
+        <v>0.173305058811246</v>
       </c>
       <c r="AI8">
-        <v>0.1890384367302057</v>
+        <v>0.2391209315264476</v>
       </c>
       <c r="AJ8">
-        <v>-0.2598981647824835</v>
+        <v>-0.09762708299473212</v>
       </c>
       <c r="AK8">
-        <v>-0.6575511024057052</v>
+        <v>-0.1538513691664469</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1460,13 +1463,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0135</v>
+        <v>0.0605</v>
       </c>
       <c r="E9">
-        <v>-0.0155</v>
+        <v>0.07139999999999999</v>
       </c>
       <c r="F9">
-        <v>0.21</v>
+        <v>0.155</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1481,28 +1484,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>728.2</v>
+        <v>1045.4</v>
       </c>
       <c r="L9">
-        <v>0.4972006008466476</v>
+        <v>0.5326878980891721</v>
       </c>
       <c r="M9">
-        <v>363.6</v>
+        <v>460.5</v>
       </c>
       <c r="N9">
-        <v>0.02842090452889771</v>
+        <v>0.04541420118343195</v>
       </c>
       <c r="O9">
-        <v>0.4993133754463059</v>
+        <v>0.4405012435431414</v>
       </c>
       <c r="P9">
-        <v>363.6</v>
+        <v>460.5</v>
       </c>
       <c r="Q9">
-        <v>0.02842090452889771</v>
+        <v>0.04541420118343195</v>
       </c>
       <c r="R9">
-        <v>0.4993133754463059</v>
+        <v>0.4405012435431414</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1511,55 +1514,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>866.1</v>
+        <v>808.5</v>
       </c>
       <c r="V9">
-        <v>0.06769896978129349</v>
+        <v>0.07973372781065088</v>
       </c>
       <c r="W9">
-        <v>0.08884171485737989</v>
+        <v>0.1237013371198675</v>
       </c>
       <c r="X9">
-        <v>0.0734971861928118</v>
+        <v>0.06538574962138566</v>
       </c>
       <c r="Y9">
-        <v>0.01534452866456809</v>
+        <v>0.05831558749848183</v>
       </c>
       <c r="Z9">
-        <v>0.1649937476765014</v>
+        <v>0.214591101440084</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.07120618682983026</v>
+        <v>0.06168459012029121</v>
       </c>
       <c r="AC9">
-        <v>-0.07120618682983026</v>
+        <v>-0.06168459012029121</v>
       </c>
       <c r="AD9">
-        <v>1560.4</v>
+        <v>2526.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>1560.4</v>
+        <v>2526.5</v>
       </c>
       <c r="AG9">
-        <v>694.3000000000001</v>
+        <v>1718</v>
       </c>
       <c r="AH9">
-        <v>0.108709888670596</v>
+        <v>0.199463150830932</v>
       </c>
       <c r="AI9">
-        <v>0.1557689620061094</v>
+        <v>0.2191639413943563</v>
       </c>
       <c r="AJ9">
-        <v>0.05147653046850094</v>
+        <v>0.144881092933041</v>
       </c>
       <c r="AK9">
-        <v>0.07586900221826409</v>
+        <v>0.1602701643748717</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1585,10 +1588,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0278</v>
+        <v>0.0558</v>
       </c>
       <c r="E10">
-        <v>0.0103</v>
+        <v>0.057</v>
+      </c>
+      <c r="F10">
+        <v>0.0781</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1603,85 +1609,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>975.8</v>
+        <v>1146</v>
       </c>
       <c r="L10">
-        <v>0.5579826166514181</v>
+        <v>0.5568242553811769</v>
       </c>
       <c r="M10">
-        <v>525.7</v>
+        <v>618.4</v>
       </c>
       <c r="N10">
-        <v>0.0405645235964073</v>
+        <v>0.04737825993686984</v>
       </c>
       <c r="O10">
-        <v>0.5387374461979915</v>
+        <v>0.5396160558464224</v>
       </c>
       <c r="P10">
-        <v>511.5</v>
+        <v>591.9</v>
       </c>
       <c r="Q10">
-        <v>0.03946881076576438</v>
+        <v>0.04534798198032546</v>
       </c>
       <c r="R10">
-        <v>0.5241852838696455</v>
+        <v>0.5164921465968586</v>
       </c>
       <c r="S10">
-        <v>14.20000000000005</v>
+        <v>26.5</v>
       </c>
       <c r="T10">
-        <v>0.02701160357618422</v>
+        <v>0.04285252263906857</v>
       </c>
       <c r="U10">
-        <v>1946.5</v>
+        <v>1344.4</v>
       </c>
       <c r="V10">
-        <v>0.1501975369610173</v>
+        <v>0.103000214519935</v>
       </c>
       <c r="W10">
-        <v>0.09327088510800993</v>
+        <v>0.1138825399980125</v>
       </c>
       <c r="X10">
-        <v>0.07428953257635396</v>
+        <v>0.06885826310639191</v>
       </c>
       <c r="Y10">
-        <v>0.01898135253165598</v>
+        <v>0.04502427689162061</v>
       </c>
       <c r="Z10">
-        <v>0.1792464433602558</v>
+        <v>0.2037077361627999</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.07138294483304684</v>
+        <v>0.06207477421046947</v>
       </c>
       <c r="AC10">
-        <v>-0.07138294483304684</v>
+        <v>-0.06207477421046947</v>
       </c>
       <c r="AD10">
-        <v>1986.7</v>
+        <v>5808</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1986.7</v>
+        <v>5808</v>
       </c>
       <c r="AG10">
-        <v>40.20000000000005</v>
+        <v>4463.6</v>
       </c>
       <c r="AH10">
-        <v>0.1329225293216381</v>
+        <v>0.3079468091875039</v>
       </c>
       <c r="AI10">
-        <v>0.1648754740781928</v>
+        <v>0.3567063621232873</v>
       </c>
       <c r="AJ10">
-        <v>0.003092355267004111</v>
+        <v>0.2548298698332953</v>
       </c>
       <c r="AK10">
-        <v>0.003978937366378973</v>
+        <v>0.2988104084242096</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1707,13 +1713,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.129</v>
+        <v>0.141</v>
       </c>
       <c r="E11">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="F11">
-        <v>0.22</v>
+        <v>0.09789999999999999</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1728,85 +1734,85 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>4466.3</v>
+        <v>5282.7</v>
       </c>
       <c r="L11">
-        <v>0.5564442783280384</v>
+        <v>0.5927559161140471</v>
       </c>
       <c r="M11">
-        <v>2383.9</v>
+        <v>2482.6</v>
       </c>
       <c r="N11">
-        <v>0.03996854692142095</v>
+        <v>0.04036682330368613</v>
       </c>
       <c r="O11">
-        <v>0.5337527707498376</v>
+        <v>0.4699490790694154</v>
       </c>
       <c r="P11">
-        <v>2383.9</v>
+        <v>2076.3</v>
       </c>
       <c r="Q11">
-        <v>0.03996854692142095</v>
+        <v>0.03376042665972911</v>
       </c>
       <c r="R11">
-        <v>0.5337527707498376</v>
+        <v>0.3930376512010904</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>406.3000000000002</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>0.1636590671070652</v>
       </c>
       <c r="U11">
-        <v>12440.3</v>
+        <v>9888.4</v>
       </c>
       <c r="V11">
-        <v>0.2085744847797949</v>
+        <v>0.1607843774897969</v>
       </c>
       <c r="W11">
-        <v>0.1048968951101508</v>
+        <v>0.1221735782031624</v>
       </c>
       <c r="X11">
-        <v>0.09009425074104868</v>
+        <v>0.07693348841903509</v>
       </c>
       <c r="Y11">
-        <v>0.0148026443691021</v>
+        <v>0.0452400897841273</v>
       </c>
       <c r="Z11">
-        <v>0.1419966033329795</v>
+        <v>0.1307442007851606</v>
       </c>
       <c r="AA11">
         <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.0729422727057177</v>
+        <v>0.06267121698337612</v>
       </c>
       <c r="AC11">
-        <v>-0.0729422727057177</v>
+        <v>-0.06267121698337612</v>
       </c>
       <c r="AD11">
-        <v>46417.5</v>
+        <v>55371.5</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>46417.5</v>
+        <v>55371.5</v>
       </c>
       <c r="AG11">
-        <v>33977.2</v>
+        <v>45483.1</v>
       </c>
       <c r="AH11">
-        <v>0.4376453750121392</v>
+        <v>0.4737769791867206</v>
       </c>
       <c r="AI11">
-        <v>0.5165868707305835</v>
+        <v>0.5513683761909314</v>
       </c>
       <c r="AJ11">
-        <v>0.3629205226144394</v>
+        <v>0.4251388757768678</v>
       </c>
       <c r="AK11">
-        <v>0.4389030910469567</v>
+        <v>0.5023691918901844</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1832,10 +1838,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0645</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="E12">
-        <v>0.0119</v>
+        <v>0.0382</v>
+      </c>
+      <c r="F12">
+        <v>0.09699999999999999</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1850,85 +1859,85 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>384.3</v>
+        <v>443.8</v>
       </c>
       <c r="L12">
-        <v>0.4659876318661331</v>
+        <v>0.4933852140077821</v>
       </c>
       <c r="M12">
-        <v>428.6</v>
+        <v>493.2</v>
       </c>
       <c r="N12">
-        <v>0.09288314840499308</v>
+        <v>0.1157393283739704</v>
       </c>
       <c r="O12">
-        <v>1.115274525110591</v>
+        <v>1.111311401532222</v>
       </c>
       <c r="P12">
-        <v>291.5</v>
+        <v>226.6</v>
       </c>
       <c r="Q12">
-        <v>0.06317180998613038</v>
+        <v>0.05317626076549409</v>
       </c>
       <c r="R12">
-        <v>0.7585219880301848</v>
+        <v>0.5105903560162235</v>
       </c>
       <c r="S12">
-        <v>137.1</v>
+        <v>266.6</v>
       </c>
       <c r="T12">
-        <v>0.3198786747550164</v>
+        <v>0.540551500405515</v>
       </c>
       <c r="U12">
-        <v>1002</v>
+        <v>766.8</v>
       </c>
       <c r="V12">
-        <v>0.2171463245492372</v>
+        <v>0.1799450871799685</v>
       </c>
       <c r="W12">
-        <v>0.08637702007147513</v>
+        <v>0.1009967684675254</v>
       </c>
       <c r="X12">
-        <v>0.08964813168449112</v>
+        <v>0.08060651053984261</v>
       </c>
       <c r="Y12">
-        <v>-0.003271111613015992</v>
+        <v>0.02039025792768277</v>
       </c>
       <c r="Z12">
-        <v>0.1112279991907748</v>
+        <v>0.1304184554801125</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.07422301751205507</v>
+        <v>0.06397926354084671</v>
       </c>
       <c r="AC12">
-        <v>-0.07422301751205507</v>
+        <v>-0.06397926354084671</v>
       </c>
       <c r="AD12">
-        <v>3509.7</v>
+        <v>4719.2</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>3509.7</v>
+        <v>4719.2</v>
       </c>
       <c r="AG12">
-        <v>2507.7</v>
+        <v>3952.4</v>
       </c>
       <c r="AH12">
-        <v>0.4320109304415258</v>
+        <v>0.5254941261622403</v>
       </c>
       <c r="AI12">
-        <v>0.4440466099014411</v>
+        <v>0.5169403336583015</v>
       </c>
       <c r="AJ12">
-        <v>0.3521012061049409</v>
+        <v>0.4811960505009922</v>
       </c>
       <c r="AK12">
-        <v>0.3633347339138498</v>
+        <v>0.4726450856821688</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ12"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.115</v>
+        <v>0.101</v>
       </c>
       <c r="E2">
-        <v>0.12</v>
+        <v>0.1355</v>
       </c>
       <c r="F2">
-        <v>0.09744999999999998</v>
+        <v>0.0687</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>18334.1</v>
+        <v>17184.5</v>
       </c>
       <c r="L2">
-        <v>0.5761725931396426</v>
+        <v>0.596768984473484</v>
       </c>
       <c r="M2">
-        <v>9386.207</v>
+        <v>8777.200000000001</v>
       </c>
       <c r="N2">
-        <v>0.0357187293911168</v>
+        <v>0.03948398926304681</v>
       </c>
       <c r="O2">
-        <v>0.5119535183074163</v>
+        <v>0.5107626058366551</v>
       </c>
       <c r="P2">
-        <v>8562.227000000001</v>
+        <v>8622</v>
       </c>
       <c r="Q2">
-        <v>0.03258311575680291</v>
+        <v>0.03878582639406526</v>
       </c>
       <c r="R2">
-        <v>0.4670110340840293</v>
+        <v>0.5017312112659664</v>
       </c>
       <c r="S2">
-        <v>823.9800000000002</v>
+        <v>155.1999999999999</v>
       </c>
       <c r="T2">
-        <v>0.08778625913534617</v>
+        <v>0.01768217654832975</v>
       </c>
       <c r="U2">
-        <v>28854</v>
+        <v>28847.4</v>
       </c>
       <c r="V2">
-        <v>0.1098024172971344</v>
+        <v>0.1297692238831081</v>
       </c>
       <c r="W2">
-        <v>0.1229374576615149</v>
+        <v>0.1379206830992962</v>
       </c>
       <c r="X2">
-        <v>0.06712200636388879</v>
+        <v>0.06929261382466284</v>
       </c>
       <c r="Y2">
-        <v>0.05581545129762615</v>
+        <v>0.06862806927463339</v>
       </c>
       <c r="Z2">
-        <v>0.2005471409782022</v>
+        <v>0.1791293323745232</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06139199548169854</v>
+        <v>0.06589864492541066</v>
       </c>
       <c r="AC2">
-        <v>-0.06139199548169854</v>
+        <v>-0.06589864492541066</v>
       </c>
       <c r="AD2">
-        <v>92402</v>
+        <v>78328.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>92402</v>
+        <v>78328.7</v>
       </c>
       <c r="AG2">
-        <v>63548</v>
+        <v>49481.3</v>
       </c>
       <c r="AH2">
-        <v>0.2601531435476519</v>
+        <v>0.2605516348530934</v>
       </c>
       <c r="AI2">
-        <v>0.3916804465399554</v>
+        <v>0.3670280310420995</v>
       </c>
       <c r="AJ2">
-        <v>0.194735927626436</v>
+        <v>0.1820644715007414</v>
       </c>
       <c r="AK2">
-        <v>0.3069096198789034</v>
+        <v>0.2680954238592156</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bank AlJazira (SASE:1020)</t>
+          <t>The Saudi National Bank (SASE:1180)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0425</v>
+        <v>0.134</v>
       </c>
       <c r="E3">
-        <v>0.0132</v>
+        <v>0.14</v>
       </c>
       <c r="F3">
-        <v>-0.017</v>
+        <v>0.0378</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>262.5</v>
+        <v>5495.3</v>
       </c>
       <c r="L3">
-        <v>0.3222836095764273</v>
+        <v>0.6015917500492632</v>
       </c>
       <c r="M3">
-        <v>13.127</v>
+        <v>2914.2</v>
       </c>
       <c r="N3">
-        <v>0.00318299750248539</v>
+        <v>0.05509988769016097</v>
       </c>
       <c r="O3">
-        <v>0.05000761904761904</v>
+        <v>0.5303077175040488</v>
       </c>
       <c r="P3">
-        <v>0.027</v>
+        <v>2881.1</v>
       </c>
       <c r="Q3">
-        <v>6.546882956281369e-06</v>
+        <v>0.05447405340200494</v>
       </c>
       <c r="R3">
-        <v>0.0001028571428571429</v>
+        <v>0.5242843884774261</v>
       </c>
       <c r="S3">
-        <v>13.1</v>
+        <v>33.09999999999991</v>
       </c>
       <c r="T3">
-        <v>0.9979431705644854</v>
+        <v>0.0113581772012902</v>
       </c>
       <c r="U3">
-        <v>613.9</v>
+        <v>11757.5</v>
       </c>
       <c r="V3">
-        <v>0.148856720254116</v>
+        <v>0.2223035239575416</v>
       </c>
       <c r="W3">
-        <v>0.07211934721688004</v>
+        <v>0.1224423861481661</v>
       </c>
       <c r="X3">
-        <v>0.08460486055035688</v>
+        <v>0.08228895453646659</v>
       </c>
       <c r="Y3">
-        <v>-0.01248551333347683</v>
+        <v>0.04015343161169956</v>
       </c>
       <c r="Z3">
-        <v>0.1253211884356777</v>
+        <v>0.112361817204473</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06036560673504222</v>
+        <v>0.06557707195306625</v>
       </c>
       <c r="AC3">
-        <v>-0.06036560673504222</v>
+        <v>-0.06557707195306625</v>
       </c>
       <c r="AD3">
-        <v>5497.1</v>
+        <v>53285.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5497.1</v>
+        <v>53285.1</v>
       </c>
       <c r="AG3">
-        <v>4883.200000000001</v>
+        <v>41527.6</v>
       </c>
       <c r="AH3">
-        <v>0.5713528457988608</v>
+        <v>0.5018634417868697</v>
       </c>
       <c r="AI3">
-        <v>0.5579849163088604</v>
+        <v>0.5207325129584314</v>
       </c>
       <c r="AJ3">
-        <v>0.5421380435868685</v>
+        <v>0.4398318099494794</v>
       </c>
       <c r="AK3">
-        <v>0.5286107081772716</v>
+        <v>0.4585153754511719</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Saudi Awwal Bank (SASE:1060)</t>
+          <t>Banque Saudi Fransi (SASE:1050)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.118</v>
+        <v>0.0803</v>
       </c>
       <c r="E4">
-        <v>0.124</v>
+        <v>0.295</v>
       </c>
       <c r="F4">
-        <v>0.144</v>
+        <v>0.0328</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1713.3</v>
+        <v>1135</v>
       </c>
       <c r="L4">
-        <v>0.5597373321572087</v>
+        <v>0.5292362212067518</v>
       </c>
       <c r="M4">
-        <v>932.6800000000001</v>
+        <v>672.3</v>
       </c>
       <c r="N4">
-        <v>0.04491142239407525</v>
+        <v>0.06423596181958895</v>
       </c>
       <c r="O4">
-        <v>0.5443763497344307</v>
+        <v>0.5923348017621145</v>
       </c>
       <c r="P4">
-        <v>922.7</v>
+        <v>639.5</v>
       </c>
       <c r="Q4">
-        <v>0.04443085457285804</v>
+        <v>0.06110203418656424</v>
       </c>
       <c r="R4">
-        <v>0.5385513336835347</v>
+        <v>0.5634361233480176</v>
       </c>
       <c r="S4">
-        <v>9.980000000000018</v>
+        <v>32.79999999999995</v>
       </c>
       <c r="T4">
-        <v>0.01070034738602738</v>
+        <v>0.04878774356685997</v>
       </c>
       <c r="U4">
-        <v>1550.9</v>
+        <v>1598</v>
       </c>
       <c r="V4">
-        <v>0.07468062464186141</v>
+        <v>0.1526834255357774</v>
       </c>
       <c r="W4">
-        <v>0.1206846758003733</v>
+        <v>0.1083604632290463</v>
       </c>
       <c r="X4">
-        <v>0.07026738011906988</v>
+        <v>0.0794233639855399</v>
       </c>
       <c r="Y4">
-        <v>0.05041729568130345</v>
+        <v>0.02893709924350645</v>
       </c>
       <c r="Z4">
-        <v>0.1591499937606589</v>
+        <v>0.1435677036263464</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0606049642191074</v>
+        <v>0.06561816448051858</v>
       </c>
       <c r="AC4">
-        <v>-0.0606049642191074</v>
+        <v>-0.06561816448051858</v>
       </c>
       <c r="AD4">
-        <v>10891</v>
+        <v>8688.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>10891</v>
+        <v>8688.9</v>
       </c>
       <c r="AG4">
-        <v>9340.1</v>
+        <v>7090.9</v>
       </c>
       <c r="AH4">
-        <v>0.3440193820854694</v>
+        <v>0.4536100234925607</v>
       </c>
       <c r="AI4">
-        <v>0.4237759679998754</v>
+        <v>0.4139286275742808</v>
       </c>
       <c r="AJ4">
-        <v>0.3102281181909975</v>
+        <v>0.4038787947827077</v>
       </c>
       <c r="AK4">
-        <v>0.3867696384943476</v>
+        <v>0.3656365858311891</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Alinma Bank (SASE:1150)</t>
+          <t>Riyad Bank (SASE:1010)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.128</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E5">
         <v>0.131</v>
       </c>
       <c r="F5">
-        <v>0.09960000000000001</v>
+        <v>0.0687</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +984,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1167.6</v>
+        <v>2406</v>
       </c>
       <c r="L5">
-        <v>0.5550484883057615</v>
+        <v>0.5940740740740741</v>
       </c>
       <c r="M5">
-        <v>601.8</v>
+        <v>1233.1</v>
       </c>
       <c r="N5">
-        <v>0.02828007518796992</v>
+        <v>0.05404611736655022</v>
       </c>
       <c r="O5">
-        <v>0.5154162384378211</v>
+        <v>0.5125103906899418</v>
       </c>
       <c r="P5">
-        <v>557.4</v>
+        <v>1233.1</v>
       </c>
       <c r="Q5">
-        <v>0.02619360902255639</v>
+        <v>0.05404611736655022</v>
       </c>
       <c r="R5">
-        <v>0.4773895169578623</v>
+        <v>0.5125103906899418</v>
       </c>
       <c r="S5">
-        <v>44.39999999999998</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.07377866400797604</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>2178.5</v>
+        <v>8566.200000000001</v>
       </c>
       <c r="V5">
-        <v>0.1023731203007519</v>
+        <v>0.3754519913918924</v>
       </c>
       <c r="W5">
-        <v>0.140131057823864</v>
+        <v>0.1570824193042933</v>
       </c>
       <c r="X5">
-        <v>0.06147669110453449</v>
+        <v>0.06929261382466284</v>
       </c>
       <c r="Y5">
-        <v>0.07865436671932954</v>
+        <v>0.0877898054796305</v>
       </c>
       <c r="Z5">
-        <v>0.1912241948239657</v>
+        <v>0.3050962371464085</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06093777334913664</v>
+        <v>0.0658605022125916</v>
       </c>
       <c r="AC5">
-        <v>-0.06093777334913664</v>
+        <v>-0.0658605022125916</v>
       </c>
       <c r="AD5">
-        <v>611.4</v>
+        <v>4641.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>611.4</v>
+        <v>4641.4</v>
       </c>
       <c r="AG5">
-        <v>-1567.1</v>
+        <v>-3924.800000000001</v>
       </c>
       <c r="AH5">
-        <v>0.02792877568360178</v>
+        <v>0.1690418871621548</v>
       </c>
       <c r="AI5">
-        <v>0.06413376410858894</v>
+        <v>0.2160287827378043</v>
       </c>
       <c r="AJ5">
-        <v>-0.0794961674842362</v>
+        <v>-0.2077614089323431</v>
       </c>
       <c r="AK5">
-        <v>-0.2130746325478945</v>
+        <v>-0.3038029553599765</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Al Rajhi Banking and Investment Corporation (SASE:1120)</t>
+          <t>Arab National Bank (SASE:1080)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,13 +1088,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.112</v>
+        <v>0.0859</v>
       </c>
       <c r="E6">
-        <v>0.116</v>
-      </c>
-      <c r="F6">
-        <v>0.068</v>
+        <v>0.0142</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,85 +1106,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>4494.2</v>
+        <v>1240.5</v>
       </c>
       <c r="L6">
-        <v>0.6410303955269652</v>
+        <v>0.5316276677809205</v>
       </c>
       <c r="M6">
-        <v>2559.7</v>
+        <v>602.9000000000001</v>
       </c>
       <c r="N6">
-        <v>0.02764648956438714</v>
+        <v>0.05368751001798786</v>
       </c>
       <c r="O6">
-        <v>0.5695563170308398</v>
+        <v>0.4860137041515519</v>
       </c>
       <c r="P6">
-        <v>2559.7</v>
+        <v>576.7</v>
       </c>
       <c r="Q6">
-        <v>0.02764648956438714</v>
+        <v>0.0513544319578265</v>
       </c>
       <c r="R6">
-        <v>0.5695563170308398</v>
+        <v>0.4648931882305523</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>26.20000000000005</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.04345662630618683</v>
       </c>
       <c r="U6">
-        <v>3805.6</v>
+        <v>950</v>
       </c>
       <c r="V6">
-        <v>0.04110305140689601</v>
+        <v>0.08459634187607973</v>
       </c>
       <c r="W6">
-        <v>0.1960922910449064</v>
+        <v>0.1379206830992962</v>
       </c>
       <c r="X6">
-        <v>0.0612259067063206</v>
+        <v>0.06829776778573982</v>
       </c>
       <c r="Y6">
-        <v>0.1348663843385858</v>
+        <v>0.06962291531355641</v>
       </c>
       <c r="Z6">
-        <v>0.4063795132186807</v>
+        <v>0.217824370116595</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06101889911994734</v>
+        <v>0.06589864492541066</v>
       </c>
       <c r="AC6">
-        <v>-0.06101889911994734</v>
+        <v>-0.06589864492541066</v>
       </c>
       <c r="AD6">
-        <v>1350.8</v>
+        <v>1593.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1350.8</v>
+        <v>1593.3</v>
       </c>
       <c r="AG6">
-        <v>-2454.8</v>
+        <v>643.3</v>
       </c>
       <c r="AH6">
-        <v>0.01437975847796835</v>
+        <v>0.1242523258806373</v>
       </c>
       <c r="AI6">
-        <v>0.04719380624965062</v>
+        <v>0.1409214331832695</v>
       </c>
       <c r="AJ6">
-        <v>-0.02723560999423068</v>
+        <v>0.0541813005870413</v>
       </c>
       <c r="AK6">
-        <v>-0.09891686277038136</v>
+        <v>0.0621167791585798</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1204,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bank Albilad (SASE:1140)</t>
+          <t>Alinma Bank (SASE:1150)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1213,13 +1210,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.12</v>
+        <v>0.137</v>
       </c>
       <c r="E7">
-        <v>0.187</v>
+        <v>0.128</v>
       </c>
       <c r="F7">
-        <v>0.153</v>
+        <v>0.117</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1234,85 +1231,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>613.7</v>
+        <v>1500.1</v>
       </c>
       <c r="L7">
-        <v>0.4698361659776451</v>
+        <v>0.5875832354093223</v>
       </c>
       <c r="M7">
-        <v>146.2</v>
+        <v>490.6</v>
       </c>
       <c r="N7">
-        <v>0.01207595794064444</v>
+        <v>0.02544883000741782</v>
       </c>
       <c r="O7">
-        <v>0.2382271468144044</v>
+        <v>0.327044863675755</v>
       </c>
       <c r="P7">
-        <v>133.3</v>
+        <v>490.6</v>
       </c>
       <c r="Q7">
-        <v>0.01101043223999934</v>
+        <v>0.02544883000741782</v>
       </c>
       <c r="R7">
-        <v>0.2172071044484276</v>
+        <v>0.327044863675755</v>
       </c>
       <c r="S7">
-        <v>12.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.08823529411764709</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1041.1</v>
+        <v>1566.8</v>
       </c>
       <c r="V7">
-        <v>0.08599370596446594</v>
+        <v>0.08127441266942975</v>
       </c>
       <c r="W7">
-        <v>0.1768791791560987</v>
+        <v>0.1681387164025197</v>
       </c>
       <c r="X7">
-        <v>0.0621579051222878</v>
+        <v>0.06728963503651691</v>
       </c>
       <c r="Y7">
-        <v>0.1147212740338109</v>
+        <v>0.1008490813660028</v>
       </c>
       <c r="Z7">
-        <v>0.5421716752448945</v>
+        <v>0.3471249677077244</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06119348387358364</v>
+        <v>0.06594173401599827</v>
       </c>
       <c r="AC7">
-        <v>-0.06119348387358364</v>
+        <v>-0.06594173401599827</v>
       </c>
       <c r="AD7">
-        <v>812.9</v>
+        <v>1532.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>812.9</v>
+        <v>1532.8</v>
       </c>
       <c r="AG7">
-        <v>-228.1999999999999</v>
+        <v>-34</v>
       </c>
       <c r="AH7">
-        <v>0.06291990464101055</v>
+        <v>0.07365441815988889</v>
       </c>
       <c r="AI7">
-        <v>0.1726195532149834</v>
+        <v>0.1225034565987069</v>
       </c>
       <c r="AJ7">
-        <v>-0.01921117986277728</v>
+        <v>-0.001766793633307178</v>
       </c>
       <c r="AK7">
-        <v>-0.06221204438265039</v>
+        <v>-0.003106299392444384</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1329,7 +1326,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Riyad Bank (SASE:1010)</t>
+          <t>Al Rajhi Banking and Investment Corporation (SASE:1120)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,13 +1335,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.131</v>
+        <v>0.101</v>
       </c>
       <c r="E8">
-        <v>0.172</v>
+        <v>0.336</v>
       </c>
       <c r="F8">
-        <v>0.0706</v>
+        <v>0.149</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1359,85 +1356,85 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>2164.9</v>
+        <v>4902.4</v>
       </c>
       <c r="L8">
-        <v>0.5863441850387303</v>
+        <v>0.6473951799273687</v>
       </c>
       <c r="M8">
-        <v>1078</v>
+        <v>2561</v>
       </c>
       <c r="N8">
-        <v>0.04694774341621047</v>
+        <v>0.02540901469377226</v>
       </c>
       <c r="O8">
-        <v>0.4979444778049794</v>
+        <v>0.5223971932114883</v>
       </c>
       <c r="P8">
-        <v>1033.8</v>
+        <v>2561</v>
       </c>
       <c r="Q8">
-        <v>0.04502279883458106</v>
+        <v>0.02540901469377226</v>
       </c>
       <c r="R8">
-        <v>0.4775278303847753</v>
+        <v>0.5223971932114883</v>
       </c>
       <c r="S8">
-        <v>44.20000000000005</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.04100185528756962</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>6855.9</v>
+        <v>3905.1</v>
       </c>
       <c r="V8">
-        <v>0.2985798089862684</v>
+        <v>0.03874453076167515</v>
       </c>
       <c r="W8">
-        <v>0.1639901828593937</v>
+        <v>0.1797620968333358</v>
       </c>
       <c r="X8">
-        <v>0.0646848111822618</v>
+        <v>0.06642008155872563</v>
       </c>
       <c r="Y8">
-        <v>0.09930537167713191</v>
+        <v>0.1133420152746101</v>
       </c>
       <c r="Z8">
-        <v>0.4635879664507055</v>
+        <v>0.3051360368782438</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06159050708981344</v>
+        <v>0.06598310928142664</v>
       </c>
       <c r="AC8">
-        <v>-0.06159050708981344</v>
+        <v>-0.06598310928142664</v>
       </c>
       <c r="AD8">
-        <v>4813.6</v>
+        <v>2591.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>4813.6</v>
+        <v>2591.7</v>
       </c>
       <c r="AG8">
-        <v>-2042.299999999999</v>
+        <v>-1313.4</v>
       </c>
       <c r="AH8">
-        <v>0.173305058811246</v>
+        <v>0.02506899123354294</v>
       </c>
       <c r="AI8">
-        <v>0.2391209315264476</v>
+        <v>0.07614181880145016</v>
       </c>
       <c r="AJ8">
-        <v>-0.09762708299473212</v>
+        <v>-0.01320297232743854</v>
       </c>
       <c r="AK8">
-        <v>-0.1538513691664469</v>
+        <v>-0.04358719928848063</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1454,7 +1451,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arab National Bank (SASE:1080)</t>
+          <t>The Saudi Investment Bank (SASE:1030)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1463,13 +1460,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0605</v>
-      </c>
-      <c r="E9">
-        <v>0.07139999999999999</v>
-      </c>
-      <c r="F9">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1484,465 +1475,90 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>1045.4</v>
+        <v>505.2</v>
       </c>
       <c r="L9">
-        <v>0.5326878980891721</v>
+        <v>0.5012899384798571</v>
       </c>
       <c r="M9">
-        <v>460.5</v>
+        <v>303.1</v>
       </c>
       <c r="N9">
-        <v>0.04541420118343195</v>
+        <v>0.0627822196445586</v>
       </c>
       <c r="O9">
-        <v>0.4405012435431414</v>
+        <v>0.5999604117181315</v>
       </c>
       <c r="P9">
-        <v>460.5</v>
+        <v>240</v>
       </c>
       <c r="Q9">
-        <v>0.04541420118343195</v>
+        <v>0.04971208417912921</v>
       </c>
       <c r="R9">
-        <v>0.4405012435431414</v>
+        <v>0.4750593824228029</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>63.10000000000002</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>0.2081821181128341</v>
       </c>
       <c r="U9">
-        <v>808.5</v>
+        <v>503.8</v>
       </c>
       <c r="V9">
-        <v>0.07973372781065088</v>
+        <v>0.1043539500393554</v>
       </c>
       <c r="W9">
-        <v>0.1237013371198675</v>
+        <v>0.1145604208712216</v>
       </c>
       <c r="X9">
-        <v>0.06538574962138566</v>
+        <v>0.08607750623399055</v>
       </c>
       <c r="Y9">
-        <v>0.05831558749848183</v>
+        <v>0.02848291463723103</v>
       </c>
       <c r="Z9">
-        <v>0.214591101440084</v>
+        <v>0.1205170826208101</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.06168459012029121</v>
+        <v>0.06664060801757671</v>
       </c>
       <c r="AC9">
-        <v>-0.06168459012029121</v>
+        <v>-0.06664060801757671</v>
       </c>
       <c r="AD9">
-        <v>2526.5</v>
+        <v>5995.5</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>2526.5</v>
+        <v>5995.5</v>
       </c>
       <c r="AG9">
-        <v>1718</v>
+        <v>5491.7</v>
       </c>
       <c r="AH9">
-        <v>0.199463150830932</v>
+        <v>0.5539438064176361</v>
       </c>
       <c r="AI9">
-        <v>0.2191639413943563</v>
+        <v>0.5575445905481058</v>
       </c>
       <c r="AJ9">
-        <v>0.144881092933041</v>
+        <v>0.5321672561655119</v>
       </c>
       <c r="AK9">
-        <v>0.1602701643748717</v>
+        <v>0.5357965188885421</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Banque Saudi Fransi (SASE:1050)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>0.0558</v>
-      </c>
-      <c r="E10">
-        <v>0.057</v>
-      </c>
-      <c r="F10">
-        <v>0.0781</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>1146</v>
-      </c>
-      <c r="L10">
-        <v>0.5568242553811769</v>
-      </c>
-      <c r="M10">
-        <v>618.4</v>
-      </c>
-      <c r="N10">
-        <v>0.04737825993686984</v>
-      </c>
-      <c r="O10">
-        <v>0.5396160558464224</v>
-      </c>
-      <c r="P10">
-        <v>591.9</v>
-      </c>
-      <c r="Q10">
-        <v>0.04534798198032546</v>
-      </c>
-      <c r="R10">
-        <v>0.5164921465968586</v>
-      </c>
-      <c r="S10">
-        <v>26.5</v>
-      </c>
-      <c r="T10">
-        <v>0.04285252263906857</v>
-      </c>
-      <c r="U10">
-        <v>1344.4</v>
-      </c>
-      <c r="V10">
-        <v>0.103000214519935</v>
-      </c>
-      <c r="W10">
-        <v>0.1138825399980125</v>
-      </c>
-      <c r="X10">
-        <v>0.06885826310639191</v>
-      </c>
-      <c r="Y10">
-        <v>0.04502427689162061</v>
-      </c>
-      <c r="Z10">
-        <v>0.2037077361627999</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0.06207477421046947</v>
-      </c>
-      <c r="AC10">
-        <v>-0.06207477421046947</v>
-      </c>
-      <c r="AD10">
-        <v>5808</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>5808</v>
-      </c>
-      <c r="AG10">
-        <v>4463.6</v>
-      </c>
-      <c r="AH10">
-        <v>0.3079468091875039</v>
-      </c>
-      <c r="AI10">
-        <v>0.3567063621232873</v>
-      </c>
-      <c r="AJ10">
-        <v>0.2548298698332953</v>
-      </c>
-      <c r="AK10">
-        <v>0.2988104084242096</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>The Saudi National Bank (SASE:1180)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>0.141</v>
-      </c>
-      <c r="E11">
-        <v>0.16</v>
-      </c>
-      <c r="F11">
-        <v>0.09789999999999999</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>5282.7</v>
-      </c>
-      <c r="L11">
-        <v>0.5927559161140471</v>
-      </c>
-      <c r="M11">
-        <v>2482.6</v>
-      </c>
-      <c r="N11">
-        <v>0.04036682330368613</v>
-      </c>
-      <c r="O11">
-        <v>0.4699490790694154</v>
-      </c>
-      <c r="P11">
-        <v>2076.3</v>
-      </c>
-      <c r="Q11">
-        <v>0.03376042665972911</v>
-      </c>
-      <c r="R11">
-        <v>0.3930376512010904</v>
-      </c>
-      <c r="S11">
-        <v>406.3000000000002</v>
-      </c>
-      <c r="T11">
-        <v>0.1636590671070652</v>
-      </c>
-      <c r="U11">
-        <v>9888.4</v>
-      </c>
-      <c r="V11">
-        <v>0.1607843774897969</v>
-      </c>
-      <c r="W11">
-        <v>0.1221735782031624</v>
-      </c>
-      <c r="X11">
-        <v>0.07693348841903509</v>
-      </c>
-      <c r="Y11">
-        <v>0.0452400897841273</v>
-      </c>
-      <c r="Z11">
-        <v>0.1307442007851606</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.06267121698337612</v>
-      </c>
-      <c r="AC11">
-        <v>-0.06267121698337612</v>
-      </c>
-      <c r="AD11">
-        <v>55371.5</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>55371.5</v>
-      </c>
-      <c r="AG11">
-        <v>45483.1</v>
-      </c>
-      <c r="AH11">
-        <v>0.4737769791867206</v>
-      </c>
-      <c r="AI11">
-        <v>0.5513683761909314</v>
-      </c>
-      <c r="AJ11">
-        <v>0.4251388757768678</v>
-      </c>
-      <c r="AK11">
-        <v>0.5023691918901844</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>The Saudi Investment Bank (SASE:1030)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.06909999999999999</v>
-      </c>
-      <c r="E12">
-        <v>0.0382</v>
-      </c>
-      <c r="F12">
-        <v>0.09699999999999999</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>443.8</v>
-      </c>
-      <c r="L12">
-        <v>0.4933852140077821</v>
-      </c>
-      <c r="M12">
-        <v>493.2</v>
-      </c>
-      <c r="N12">
-        <v>0.1157393283739704</v>
-      </c>
-      <c r="O12">
-        <v>1.111311401532222</v>
-      </c>
-      <c r="P12">
-        <v>226.6</v>
-      </c>
-      <c r="Q12">
-        <v>0.05317626076549409</v>
-      </c>
-      <c r="R12">
-        <v>0.5105903560162235</v>
-      </c>
-      <c r="S12">
-        <v>266.6</v>
-      </c>
-      <c r="T12">
-        <v>0.540551500405515</v>
-      </c>
-      <c r="U12">
-        <v>766.8</v>
-      </c>
-      <c r="V12">
-        <v>0.1799450871799685</v>
-      </c>
-      <c r="W12">
-        <v>0.1009967684675254</v>
-      </c>
-      <c r="X12">
-        <v>0.08060651053984261</v>
-      </c>
-      <c r="Y12">
-        <v>0.02039025792768277</v>
-      </c>
-      <c r="Z12">
-        <v>0.1304184554801125</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.06397926354084671</v>
-      </c>
-      <c r="AC12">
-        <v>-0.06397926354084671</v>
-      </c>
-      <c r="AD12">
-        <v>4719.2</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>4719.2</v>
-      </c>
-      <c r="AG12">
-        <v>3952.4</v>
-      </c>
-      <c r="AH12">
-        <v>0.5254941261622403</v>
-      </c>
-      <c r="AI12">
-        <v>0.5169403336583015</v>
-      </c>
-      <c r="AJ12">
-        <v>0.4811960505009922</v>
-      </c>
-      <c r="AK12">
-        <v>0.4726450856821688</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.101</v>
+        <v>0.10045</v>
       </c>
       <c r="E2">
-        <v>0.1355</v>
+        <v>0.256</v>
       </c>
       <c r="F2">
-        <v>0.0687</v>
+        <v>0.0823</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,97 +603,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1.957136629930658E-05</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1.732231523666562E-05</v>
       </c>
       <c r="K2">
-        <v>17184.5</v>
+        <v>20293.8</v>
       </c>
       <c r="L2">
-        <v>0.596768984473484</v>
+        <v>0.5863328267565021</v>
       </c>
       <c r="M2">
-        <v>8777.200000000001</v>
+        <v>10358.381</v>
       </c>
       <c r="N2">
-        <v>0.03948398926304681</v>
+        <v>0.04002123852638549</v>
       </c>
       <c r="O2">
-        <v>0.5107626058366551</v>
+        <v>0.5104209660093231</v>
       </c>
       <c r="P2">
-        <v>8622</v>
+        <v>10032.081</v>
       </c>
       <c r="Q2">
-        <v>0.03878582639406526</v>
+        <v>0.03876052701836512</v>
       </c>
       <c r="R2">
-        <v>0.5017312112659664</v>
+        <v>0.494342163616474</v>
       </c>
       <c r="S2">
-        <v>155.1999999999999</v>
+        <v>326.3</v>
       </c>
       <c r="T2">
-        <v>0.01768217654832975</v>
+        <v>0.03150106179720556</v>
       </c>
       <c r="U2">
-        <v>28847.4</v>
+        <v>35054.3</v>
       </c>
       <c r="V2">
-        <v>0.1297692238831081</v>
+        <v>0.1354378161679393</v>
       </c>
       <c r="W2">
-        <v>0.1379206830992962</v>
+        <v>0.1392322726181272</v>
       </c>
       <c r="X2">
-        <v>0.06929261382466284</v>
+        <v>0.0739909724718498</v>
       </c>
       <c r="Y2">
-        <v>0.06862806927463339</v>
+        <v>0.06524130014627741</v>
       </c>
       <c r="Z2">
-        <v>0.1791293323745232</v>
+        <v>0.1770673605458218</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06589864492541066</v>
+        <v>0.06581569864331432</v>
       </c>
       <c r="AC2">
-        <v>-0.06589864492541066</v>
+        <v>-0.06581569864331432</v>
       </c>
       <c r="AD2">
-        <v>78328.7</v>
+        <v>99658.5</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.143038062340902</v>
       </c>
       <c r="AF2">
-        <v>78328.7</v>
+        <v>99659.64303806234</v>
       </c>
       <c r="AG2">
-        <v>49481.3</v>
+        <v>64605.34303806233</v>
       </c>
       <c r="AH2">
-        <v>0.2605516348530934</v>
+        <v>0.2780047937545339</v>
       </c>
       <c r="AI2">
-        <v>0.3670280310420995</v>
+        <v>0.382127100075622</v>
       </c>
       <c r="AJ2">
-        <v>0.1820644715007414</v>
+        <v>0.1997521992296099</v>
       </c>
       <c r="AK2">
-        <v>0.2680954238592156</v>
+        <v>0.286183402383557</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>109998.3443708609</v>
+      </c>
+      <c r="AP2">
+        <v>71308.32564907541</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Saudi National Bank (SASE:1180)</t>
+          <t>Bank AlJazira (SASE:1020)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.134</v>
+        <v>0.0451</v>
       </c>
       <c r="E3">
-        <v>0.14</v>
-      </c>
-      <c r="F3">
-        <v>0.0378</v>
+        <v>0.256</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,97 +731,103 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.0007450422212184555</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.0006562371886759068</v>
       </c>
       <c r="K3">
-        <v>5495.3</v>
+        <v>328.1</v>
       </c>
       <c r="L3">
-        <v>0.6015917500492632</v>
+        <v>0.3608666959964804</v>
       </c>
       <c r="M3">
-        <v>2914.2</v>
+        <v>94.58099999999999</v>
       </c>
       <c r="N3">
-        <v>0.05509988769016097</v>
+        <v>0.01852531583586328</v>
       </c>
       <c r="O3">
-        <v>0.5303077175040488</v>
+        <v>0.2882688204815604</v>
       </c>
       <c r="P3">
-        <v>2881.1</v>
+        <v>0.981</v>
       </c>
       <c r="Q3">
-        <v>0.05447405340200494</v>
+        <v>0.0001921457251983155</v>
       </c>
       <c r="R3">
-        <v>0.5242843884774261</v>
+        <v>0.002989942090825968</v>
       </c>
       <c r="S3">
-        <v>33.09999999999991</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="T3">
-        <v>0.0113581772012902</v>
+        <v>0.9896279379579409</v>
       </c>
       <c r="U3">
-        <v>11757.5</v>
+        <v>554.4</v>
       </c>
       <c r="V3">
-        <v>0.2223035239575416</v>
+        <v>0.1085887768093233</v>
       </c>
       <c r="W3">
-        <v>0.1224423861481661</v>
+        <v>0.07534561153722501</v>
       </c>
       <c r="X3">
-        <v>0.08228895453646659</v>
+        <v>0.08508777111194168</v>
       </c>
       <c r="Y3">
-        <v>0.04015343161169956</v>
+        <v>-0.009742159574716677</v>
       </c>
       <c r="Z3">
-        <v>0.112361817204473</v>
+        <v>0.09840952544617962</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>6.457999031773101E-05</v>
       </c>
       <c r="AB3">
-        <v>0.06557707195306625</v>
+        <v>0.06401812993986501</v>
       </c>
       <c r="AC3">
-        <v>-0.06557707195306625</v>
+        <v>-0.06395354994954729</v>
       </c>
       <c r="AD3">
-        <v>53285.1</v>
+        <v>6032.4</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.143038062340902</v>
       </c>
       <c r="AF3">
-        <v>53285.1</v>
+        <v>6033.54303806234</v>
       </c>
       <c r="AG3">
-        <v>41527.6</v>
+        <v>5479.143038062341</v>
       </c>
       <c r="AH3">
-        <v>0.5018634417868697</v>
+        <v>0.5416572157451586</v>
       </c>
       <c r="AI3">
-        <v>0.5207325129584314</v>
+        <v>0.565386187971357</v>
       </c>
       <c r="AJ3">
-        <v>0.4398318099494794</v>
+        <v>0.5176502427487976</v>
       </c>
       <c r="AK3">
-        <v>0.4585153754511719</v>
+        <v>0.5415701861136994</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>6658.278145695363</v>
+      </c>
+      <c r="AP3">
+        <v>6047.619247309426</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banque Saudi Fransi (SASE:1050)</t>
+          <t>Saudi Awwal Bank (SASE:1060)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +847,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0803</v>
+        <v>0.148</v>
       </c>
       <c r="E4">
-        <v>0.295</v>
+        <v>0.321</v>
       </c>
       <c r="F4">
-        <v>0.0328</v>
+        <v>0.0823</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +868,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1135</v>
+        <v>2081.3</v>
       </c>
       <c r="L4">
-        <v>0.5292362212067518</v>
+        <v>0.5958658993959175</v>
       </c>
       <c r="M4">
-        <v>672.3</v>
+        <v>1156.2</v>
       </c>
       <c r="N4">
-        <v>0.06423596181958895</v>
+        <v>0.06277827248441674</v>
       </c>
       <c r="O4">
-        <v>0.5923348017621145</v>
+        <v>0.5555181857492912</v>
       </c>
       <c r="P4">
-        <v>639.5</v>
+        <v>1109</v>
       </c>
       <c r="Q4">
-        <v>0.06110203418656424</v>
+        <v>0.06021545077427622</v>
       </c>
       <c r="R4">
-        <v>0.5634361233480176</v>
+        <v>0.5328400518906452</v>
       </c>
       <c r="S4">
-        <v>32.79999999999995</v>
+        <v>47.20000000000005</v>
       </c>
       <c r="T4">
-        <v>0.04878774356685997</v>
+        <v>0.04082338695727387</v>
       </c>
       <c r="U4">
-        <v>1598</v>
+        <v>2418</v>
       </c>
       <c r="V4">
-        <v>0.1526834255357774</v>
+        <v>0.1312903155745716</v>
       </c>
       <c r="W4">
-        <v>0.1083604632290463</v>
+        <v>0.1405438621369582</v>
       </c>
       <c r="X4">
-        <v>0.0794233639855399</v>
+        <v>0.07870030240130524</v>
       </c>
       <c r="Y4">
-        <v>0.02893709924350645</v>
+        <v>0.06184355973565295</v>
       </c>
       <c r="Z4">
-        <v>0.1435677036263464</v>
+        <v>0.1601630564369692</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06561816448051858</v>
+        <v>0.06438835159527817</v>
       </c>
       <c r="AC4">
-        <v>-0.06561816448051858</v>
+        <v>-0.06438835159527817</v>
       </c>
       <c r="AD4">
-        <v>8688.9</v>
+        <v>14483.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>8688.9</v>
+        <v>14483.5</v>
       </c>
       <c r="AG4">
-        <v>7090.9</v>
+        <v>12065.5</v>
       </c>
       <c r="AH4">
-        <v>0.4536100234925607</v>
+        <v>0.4402185971727046</v>
       </c>
       <c r="AI4">
-        <v>0.4139286275742808</v>
+        <v>0.4583371571608951</v>
       </c>
       <c r="AJ4">
-        <v>0.4038787947827077</v>
+        <v>0.395814675209217</v>
       </c>
       <c r="AK4">
-        <v>0.3656365858311891</v>
+        <v>0.4134555086851187</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Riyad Bank (SASE:1010)</t>
+          <t>The Saudi National Bank (SASE:1180)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,13 +972,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.09470000000000001</v>
+        <v>0.134</v>
       </c>
       <c r="E5">
-        <v>0.131</v>
+        <v>0.14</v>
       </c>
       <c r="F5">
-        <v>0.0687</v>
+        <v>0.0378</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,85 +993,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>2406</v>
+        <v>5495.3</v>
       </c>
       <c r="L5">
-        <v>0.5940740740740741</v>
+        <v>0.6015917500492632</v>
       </c>
       <c r="M5">
-        <v>1233.1</v>
+        <v>2914.2</v>
       </c>
       <c r="N5">
-        <v>0.05404611736655022</v>
+        <v>0.05509988769016097</v>
       </c>
       <c r="O5">
-        <v>0.5125103906899418</v>
+        <v>0.5303077175040488</v>
       </c>
       <c r="P5">
-        <v>1233.1</v>
+        <v>2881.1</v>
       </c>
       <c r="Q5">
-        <v>0.05404611736655022</v>
+        <v>0.05447405340200494</v>
       </c>
       <c r="R5">
-        <v>0.5125103906899418</v>
+        <v>0.5242843884774261</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>33.09999999999991</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.0113581772012902</v>
       </c>
       <c r="U5">
-        <v>8566.200000000001</v>
+        <v>11757.5</v>
       </c>
       <c r="V5">
-        <v>0.3754519913918924</v>
+        <v>0.2223035239575416</v>
       </c>
       <c r="W5">
-        <v>0.1570824193042933</v>
+        <v>0.1224423861481661</v>
       </c>
       <c r="X5">
-        <v>0.06929261382466284</v>
+        <v>0.0822719138349555</v>
       </c>
       <c r="Y5">
-        <v>0.0877898054796305</v>
+        <v>0.04017047231321065</v>
       </c>
       <c r="Z5">
-        <v>0.3050962371464085</v>
+        <v>0.112361817204473</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0658605022125916</v>
+        <v>0.06556858335666597</v>
       </c>
       <c r="AC5">
-        <v>-0.0658605022125916</v>
+        <v>-0.06556858335666597</v>
       </c>
       <c r="AD5">
-        <v>4641.4</v>
+        <v>53285.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>4641.4</v>
+        <v>53285.1</v>
       </c>
       <c r="AG5">
-        <v>-3924.800000000001</v>
+        <v>41527.6</v>
       </c>
       <c r="AH5">
-        <v>0.1690418871621548</v>
+        <v>0.5018634417868697</v>
       </c>
       <c r="AI5">
-        <v>0.2160287827378043</v>
+        <v>0.5207325129584314</v>
       </c>
       <c r="AJ5">
-        <v>-0.2077614089323431</v>
+        <v>0.4398318099494794</v>
       </c>
       <c r="AK5">
-        <v>-0.3038029553599765</v>
+        <v>0.4585153754511719</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1079,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Arab National Bank (SASE:1080)</t>
+          <t>Banque Saudi Fransi (SASE:1050)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,10 +1097,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0859</v>
+        <v>0.0803</v>
       </c>
       <c r="E6">
-        <v>0.0142</v>
+        <v>0.295</v>
+      </c>
+      <c r="F6">
+        <v>0.0328</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1106,85 +1118,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1240.5</v>
+        <v>1135</v>
       </c>
       <c r="L6">
-        <v>0.5316276677809205</v>
+        <v>0.5292362212067518</v>
       </c>
       <c r="M6">
-        <v>602.9000000000001</v>
+        <v>672.3</v>
       </c>
       <c r="N6">
-        <v>0.05368751001798786</v>
+        <v>0.06423596181958895</v>
       </c>
       <c r="O6">
-        <v>0.4860137041515519</v>
+        <v>0.5923348017621145</v>
       </c>
       <c r="P6">
-        <v>576.7</v>
+        <v>639.5</v>
       </c>
       <c r="Q6">
-        <v>0.0513544319578265</v>
+        <v>0.06110203418656424</v>
       </c>
       <c r="R6">
-        <v>0.4648931882305523</v>
+        <v>0.5634361233480176</v>
       </c>
       <c r="S6">
-        <v>26.20000000000005</v>
+        <v>32.79999999999995</v>
       </c>
       <c r="T6">
-        <v>0.04345662630618683</v>
+        <v>0.04878774356685997</v>
       </c>
       <c r="U6">
-        <v>950</v>
+        <v>1598</v>
       </c>
       <c r="V6">
-        <v>0.08459634187607973</v>
+        <v>0.1526834255357774</v>
       </c>
       <c r="W6">
-        <v>0.1379206830992962</v>
+        <v>0.1083604632290463</v>
       </c>
       <c r="X6">
-        <v>0.06829776778573982</v>
+        <v>0.0794076615430678</v>
       </c>
       <c r="Y6">
-        <v>0.06962291531355641</v>
+        <v>0.02895280168597854</v>
       </c>
       <c r="Z6">
-        <v>0.217824370116595</v>
+        <v>0.1435677036263464</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06589864492541066</v>
+        <v>0.06560958482334514</v>
       </c>
       <c r="AC6">
-        <v>-0.06589864492541066</v>
+        <v>-0.06560958482334514</v>
       </c>
       <c r="AD6">
-        <v>1593.3</v>
+        <v>8688.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1593.3</v>
+        <v>8688.9</v>
       </c>
       <c r="AG6">
-        <v>643.3</v>
+        <v>7090.9</v>
       </c>
       <c r="AH6">
-        <v>0.1242523258806373</v>
+        <v>0.4536100234925607</v>
       </c>
       <c r="AI6">
-        <v>0.1409214331832695</v>
+        <v>0.4139286275742808</v>
       </c>
       <c r="AJ6">
-        <v>0.0541813005870413</v>
+        <v>0.4038787947827077</v>
       </c>
       <c r="AK6">
-        <v>0.0621167791585798</v>
+        <v>0.3656365858311891</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1201,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alinma Bank (SASE:1150)</t>
+          <t>Bank Albilad (SASE:1140)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,13 +1222,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.137</v>
+        <v>0.0999</v>
       </c>
       <c r="E7">
-        <v>0.128</v>
+        <v>0.274</v>
       </c>
       <c r="F7">
-        <v>0.117</v>
+        <v>0.144</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1231,85 +1243,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1500.1</v>
+        <v>699.9</v>
       </c>
       <c r="L7">
-        <v>0.5875832354093223</v>
+        <v>0.4951889061836705</v>
       </c>
       <c r="M7">
-        <v>490.6</v>
+        <v>330.4</v>
       </c>
       <c r="N7">
-        <v>0.02544883000741782</v>
+        <v>0.02541206149965005</v>
       </c>
       <c r="O7">
-        <v>0.327044863675755</v>
+        <v>0.472067438205458</v>
       </c>
       <c r="P7">
-        <v>490.6</v>
+        <v>300.1</v>
       </c>
       <c r="Q7">
-        <v>0.02544883000741782</v>
+        <v>0.0230815970219279</v>
       </c>
       <c r="R7">
-        <v>0.327044863675755</v>
+        <v>0.4287755393627661</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>30.30000000000001</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.09170702179176758</v>
       </c>
       <c r="U7">
-        <v>1566.8</v>
+        <v>3234.5</v>
       </c>
       <c r="V7">
-        <v>0.08127441266942975</v>
+        <v>0.2487751601713622</v>
       </c>
       <c r="W7">
-        <v>0.1681387164025197</v>
+        <v>0.1796319585247542</v>
       </c>
       <c r="X7">
-        <v>0.06728963503651691</v>
+        <v>0.06700638104960351</v>
       </c>
       <c r="Y7">
-        <v>0.1008490813660028</v>
+        <v>0.1126255774751507</v>
       </c>
       <c r="Z7">
-        <v>0.3471249677077244</v>
+        <v>0.3853221013603774</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06594173401599827</v>
+        <v>0.06578001175004626</v>
       </c>
       <c r="AC7">
-        <v>-0.06594173401599827</v>
+        <v>-0.06578001175004626</v>
       </c>
       <c r="AD7">
-        <v>1532.8</v>
+        <v>813.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>1532.8</v>
+        <v>813.9</v>
       </c>
       <c r="AG7">
-        <v>-34</v>
+        <v>-2420.6</v>
       </c>
       <c r="AH7">
-        <v>0.07365441815988889</v>
+        <v>0.05891166507426387</v>
       </c>
       <c r="AI7">
-        <v>0.1225034565987069</v>
+        <v>0.1590487170969066</v>
       </c>
       <c r="AJ7">
-        <v>-0.001766793633307178</v>
+        <v>-0.2287663853474591</v>
       </c>
       <c r="AK7">
-        <v>-0.003106299392444384</v>
+        <v>-1.285638410877417</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1326,7 +1338,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Al Rajhi Banking and Investment Corporation (SASE:1120)</t>
+          <t>Riyad Bank (SASE:1010)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1335,13 +1347,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.101</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E8">
-        <v>0.336</v>
+        <v>0.131</v>
       </c>
       <c r="F8">
-        <v>0.149</v>
+        <v>0.0687</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1356,28 +1368,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>4902.4</v>
+        <v>2406</v>
       </c>
       <c r="L8">
-        <v>0.6473951799273687</v>
+        <v>0.5940740740740741</v>
       </c>
       <c r="M8">
-        <v>2561</v>
+        <v>1233.1</v>
       </c>
       <c r="N8">
-        <v>0.02540901469377226</v>
+        <v>0.05404611736655022</v>
       </c>
       <c r="O8">
-        <v>0.5223971932114883</v>
+        <v>0.5125103906899418</v>
       </c>
       <c r="P8">
-        <v>2561</v>
+        <v>1233.1</v>
       </c>
       <c r="Q8">
-        <v>0.02540901469377226</v>
+        <v>0.05404611736655022</v>
       </c>
       <c r="R8">
-        <v>0.5223971932114883</v>
+        <v>0.5125103906899418</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1386,55 +1398,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>3905.1</v>
+        <v>8566.200000000001</v>
       </c>
       <c r="V8">
-        <v>0.03874453076167515</v>
+        <v>0.3754519913918924</v>
       </c>
       <c r="W8">
-        <v>0.1797620968333358</v>
+        <v>0.1570824193042933</v>
       </c>
       <c r="X8">
-        <v>0.06642008155872563</v>
+        <v>0.06928164254239437</v>
       </c>
       <c r="Y8">
-        <v>0.1133420152746101</v>
+        <v>0.08780077676189897</v>
       </c>
       <c r="Z8">
-        <v>0.3051360368782438</v>
+        <v>0.3050962371464085</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.06598310928142664</v>
+        <v>0.06585138553658237</v>
       </c>
       <c r="AC8">
-        <v>-0.06598310928142664</v>
+        <v>-0.06585138553658237</v>
       </c>
       <c r="AD8">
-        <v>2591.7</v>
+        <v>4641.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>2591.7</v>
+        <v>4641.4</v>
       </c>
       <c r="AG8">
-        <v>-1313.4</v>
+        <v>-3924.800000000001</v>
       </c>
       <c r="AH8">
-        <v>0.02506899123354294</v>
+        <v>0.1690418871621548</v>
       </c>
       <c r="AI8">
-        <v>0.07614181880145016</v>
+        <v>0.2160287827378043</v>
       </c>
       <c r="AJ8">
-        <v>-0.01320297232743854</v>
+        <v>-0.2077614089323431</v>
       </c>
       <c r="AK8">
-        <v>-0.04358719928848063</v>
+        <v>-0.3038029553599765</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1451,114 +1463,486 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Arab National Bank (SASE:1080)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0859</v>
+      </c>
+      <c r="E9">
+        <v>0.0142</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>1240.5</v>
+      </c>
+      <c r="L9">
+        <v>0.5316276677809205</v>
+      </c>
+      <c r="M9">
+        <v>602.9000000000001</v>
+      </c>
+      <c r="N9">
+        <v>0.05368751001798786</v>
+      </c>
+      <c r="O9">
+        <v>0.4860137041515519</v>
+      </c>
+      <c r="P9">
+        <v>576.7</v>
+      </c>
+      <c r="Q9">
+        <v>0.0513544319578265</v>
+      </c>
+      <c r="R9">
+        <v>0.4648931882305523</v>
+      </c>
+      <c r="S9">
+        <v>26.20000000000005</v>
+      </c>
+      <c r="T9">
+        <v>0.04345662630618683</v>
+      </c>
+      <c r="U9">
+        <v>950</v>
+      </c>
+      <c r="V9">
+        <v>0.08459634187607973</v>
+      </c>
+      <c r="W9">
+        <v>0.1379206830992962</v>
+      </c>
+      <c r="X9">
+        <v>0.06828726110637966</v>
+      </c>
+      <c r="Y9">
+        <v>0.06963342199291657</v>
+      </c>
+      <c r="Z9">
+        <v>0.217824370116595</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.06588944372539829</v>
+      </c>
+      <c r="AC9">
+        <v>-0.06588944372539829</v>
+      </c>
+      <c r="AD9">
+        <v>1593.3</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>1593.3</v>
+      </c>
+      <c r="AG9">
+        <v>643.3</v>
+      </c>
+      <c r="AH9">
+        <v>0.1242523258806373</v>
+      </c>
+      <c r="AI9">
+        <v>0.1409214331832695</v>
+      </c>
+      <c r="AJ9">
+        <v>0.0541813005870413</v>
+      </c>
+      <c r="AK9">
+        <v>0.0621167791585798</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Alinma Bank (SASE:1150)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.137</v>
+      </c>
+      <c r="E10">
+        <v>0.128</v>
+      </c>
+      <c r="F10">
+        <v>0.117</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>1500.1</v>
+      </c>
+      <c r="L10">
+        <v>0.5875832354093223</v>
+      </c>
+      <c r="M10">
+        <v>490.6</v>
+      </c>
+      <c r="N10">
+        <v>0.02544883000741782</v>
+      </c>
+      <c r="O10">
+        <v>0.327044863675755</v>
+      </c>
+      <c r="P10">
+        <v>490.6</v>
+      </c>
+      <c r="Q10">
+        <v>0.02544883000741782</v>
+      </c>
+      <c r="R10">
+        <v>0.327044863675755</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>1566.8</v>
+      </c>
+      <c r="V10">
+        <v>0.08127441266942975</v>
+      </c>
+      <c r="W10">
+        <v>0.1681387164025197</v>
+      </c>
+      <c r="X10">
+        <v>0.06727959916508976</v>
+      </c>
+      <c r="Y10">
+        <v>0.1008591172374299</v>
+      </c>
+      <c r="Z10">
+        <v>0.3471249677077244</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.06593243733084181</v>
+      </c>
+      <c r="AC10">
+        <v>-0.06593243733084181</v>
+      </c>
+      <c r="AD10">
+        <v>1532.8</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>1532.8</v>
+      </c>
+      <c r="AG10">
+        <v>-34</v>
+      </c>
+      <c r="AH10">
+        <v>0.07365441815988889</v>
+      </c>
+      <c r="AI10">
+        <v>0.1225034565987069</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.001766793633307178</v>
+      </c>
+      <c r="AK10">
+        <v>-0.003106299392444384</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Al Rajhi Banking and Investment Corporation (SASE:1120)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.101</v>
+      </c>
+      <c r="E11">
+        <v>0.336</v>
+      </c>
+      <c r="F11">
+        <v>0.149</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>4902.4</v>
+      </c>
+      <c r="L11">
+        <v>0.6473951799273687</v>
+      </c>
+      <c r="M11">
+        <v>2561</v>
+      </c>
+      <c r="N11">
+        <v>0.02540901469377226</v>
+      </c>
+      <c r="O11">
+        <v>0.5223971932114883</v>
+      </c>
+      <c r="P11">
+        <v>2561</v>
+      </c>
+      <c r="Q11">
+        <v>0.02540901469377226</v>
+      </c>
+      <c r="R11">
+        <v>0.5223971932114883</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>3905.1</v>
+      </c>
+      <c r="V11">
+        <v>0.03874453076167515</v>
+      </c>
+      <c r="W11">
+        <v>0.1797620968333358</v>
+      </c>
+      <c r="X11">
+        <v>0.06641045177734547</v>
+      </c>
+      <c r="Y11">
+        <v>0.1133516450559903</v>
+      </c>
+      <c r="Z11">
+        <v>0.3051360368782438</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.06597372090895148</v>
+      </c>
+      <c r="AC11">
+        <v>-0.06597372090895148</v>
+      </c>
+      <c r="AD11">
+        <v>2591.7</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>2591.7</v>
+      </c>
+      <c r="AG11">
+        <v>-1313.4</v>
+      </c>
+      <c r="AH11">
+        <v>0.02506899123354294</v>
+      </c>
+      <c r="AI11">
+        <v>0.07614181880145016</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.01320297232743854</v>
+      </c>
+      <c r="AK11">
+        <v>-0.04358719928848063</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>The Saudi Investment Bank (SASE:1030)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D9">
+      <c r="D12">
         <v>0.152</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
         <v>505.2</v>
       </c>
-      <c r="L9">
+      <c r="L12">
         <v>0.5012899384798571</v>
       </c>
-      <c r="M9">
+      <c r="M12">
         <v>303.1</v>
       </c>
-      <c r="N9">
+      <c r="N12">
         <v>0.0627822196445586</v>
       </c>
-      <c r="O9">
+      <c r="O12">
         <v>0.5999604117181315</v>
       </c>
-      <c r="P9">
+      <c r="P12">
         <v>240</v>
       </c>
-      <c r="Q9">
+      <c r="Q12">
         <v>0.04971208417912921</v>
       </c>
-      <c r="R9">
+      <c r="R12">
         <v>0.4750593824228029</v>
       </c>
-      <c r="S9">
+      <c r="S12">
         <v>63.10000000000002</v>
       </c>
-      <c r="T9">
+      <c r="T12">
         <v>0.2081821181128341</v>
       </c>
-      <c r="U9">
+      <c r="U12">
         <v>503.8</v>
       </c>
-      <c r="V9">
+      <c r="V12">
         <v>0.1043539500393554</v>
       </c>
-      <c r="W9">
+      <c r="W12">
         <v>0.1145604208712216</v>
       </c>
-      <c r="X9">
-        <v>0.08607750623399055</v>
-      </c>
-      <c r="Y9">
-        <v>0.02848291463723103</v>
-      </c>
-      <c r="Z9">
+      <c r="X12">
+        <v>0.0860586962414856</v>
+      </c>
+      <c r="Y12">
+        <v>0.02850172462973598</v>
+      </c>
+      <c r="Z12">
         <v>0.1205170826208101</v>
       </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.06664060801757671</v>
-      </c>
-      <c r="AC9">
-        <v>-0.06664060801757671</v>
-      </c>
-      <c r="AD9">
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.06663221770391864</v>
+      </c>
+      <c r="AC12">
+        <v>-0.06663221770391864</v>
+      </c>
+      <c r="AD12">
         <v>5995.5</v>
       </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
         <v>5995.5</v>
       </c>
-      <c r="AG9">
+      <c r="AG12">
         <v>5491.7</v>
       </c>
-      <c r="AH9">
+      <c r="AH12">
         <v>0.5539438064176361</v>
       </c>
-      <c r="AI9">
+      <c r="AI12">
         <v>0.5575445905481058</v>
       </c>
-      <c r="AJ9">
+      <c r="AJ12">
         <v>0.5321672561655119</v>
       </c>
-      <c r="AK9">
+      <c r="AK12">
         <v>0.5357965188885421</v>
       </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
         <v>0</v>
       </c>
     </row>
